--- a/Cdd Parsing/RADAR_G7_CHERY03_APP_and_BOOT.xlsx
+++ b/Cdd Parsing/RADAR_G7_CHERY03_APP_and_BOOT.xlsx
@@ -13,10 +13,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RID" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Service'!$A$1:$K$140</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'DID'!$A$1:$Y$100</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'DTC'!$A$1:$AB$34</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'RID'!$A$1:$J$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Service'!$A$1:$L$140</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'DID'!$A$1:$AA$100</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'DTC'!$A$1:$AC$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'RID'!$A$1:$K$19</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K140"/>
+  <dimension ref="A1:L140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -450,6 +450,7 @@
     <col width="22" customWidth="1" min="9" max="9"/>
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="37" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -508,6 +509,11 @@
           <t>Security</t>
         </is>
       </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>CDD Ref</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -565,6 +571,11 @@
           <t>Locked, Unlocked_0x11, Unlocked_0x1</t>
         </is>
       </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>_2998@_2995</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -622,6 +633,11 @@
           <t>Locked, Unlocked_0x11, Unlocked_0x1</t>
         </is>
       </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>_3000@_2995</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -679,6 +695,11 @@
           <t>Locked, Unlocked_0x11, Unlocked_0x1</t>
         </is>
       </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>_3002@_2995</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -736,6 +757,11 @@
           <t>All</t>
         </is>
       </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>_3004@_2995</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -793,6 +819,11 @@
           <t>Locked, Unlocked_0x11, Unlocked_0x1</t>
         </is>
       </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>_3007@_2995</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -850,6 +881,11 @@
           <t>All</t>
         </is>
       </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>_3009@_2995</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -907,6 +943,11 @@
           <t>All</t>
         </is>
       </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>_3010@_2995</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -964,6 +1005,11 @@
           <t>All</t>
         </is>
       </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>_3011@_2995</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1021,6 +1067,11 @@
           <t>All</t>
         </is>
       </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>_3012@_2995</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1078,6 +1129,11 @@
           <t>All</t>
         </is>
       </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>_3013@_2995</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1135,6 +1191,11 @@
           <t>All</t>
         </is>
       </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>_3014@_2995</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1192,6 +1253,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>_3017@_2995</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1249,6 +1315,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>_3019@_2995</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1306,6 +1377,11 @@
           <t>Locked, Unlocked_0x1</t>
         </is>
       </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>_3021@_2995</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1363,6 +1439,11 @@
           <t>Locked, Unlocked_0x1</t>
         </is>
       </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>_3022@_2995</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1420,6 +1501,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>_3029@_2995</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1477,6 +1563,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>_3030@_2995</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1534,6 +1625,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>_3031@_2995</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1591,6 +1687,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>_3033@_2995</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1648,6 +1749,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>_3034@_2995</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1705,6 +1811,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>_3035@_2995</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1762,6 +1873,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>_3037@_2995</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1819,6 +1935,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>_3038@_2995</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -1876,6 +1997,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>_3039@_2995</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1933,6 +2059,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>_3041@_2995</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -1990,6 +2121,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>_3042@_2995</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -2047,6 +2183,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>_3043@_2995</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -2104,6 +2245,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>_3045@_2995</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -2161,6 +2307,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>_3046@_2995</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -2218,6 +2369,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>_3047@_2995</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -2275,6 +2431,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>_3049@_2995</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -2332,6 +2493,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>_3050@_2995</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -2389,6 +2555,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>_3051@_2995</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -2446,6 +2617,11 @@
           <t>All</t>
         </is>
       </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>_3004@_3053</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -2503,6 +2679,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>_3058@_3053</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -2560,6 +2741,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>_3060@_3053</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -2617,6 +2803,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>_3063@_3053</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -2674,6 +2865,11 @@
           <t>Locked, Unlocked_0x1</t>
         </is>
       </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>_3021@_3053</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -2731,6 +2927,11 @@
           <t>Locked, Unlocked_0x1</t>
         </is>
       </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>_3022@_3053</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -2788,6 +2989,11 @@
           <t>Locked, Unlocked_0x1</t>
         </is>
       </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>_3065@_3053</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -2845,6 +3051,11 @@
           <t>All</t>
         </is>
       </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>_3066@_3053</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -2902,6 +3113,11 @@
           <t>Locked, Unlocked_0x1</t>
         </is>
       </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>_3067@_3053</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -2959,6 +3175,11 @@
           <t>Locked, Unlocked_0x1</t>
         </is>
       </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>_3068@_3053</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -3016,6 +3237,11 @@
           <t>Locked, Unlocked_0x1</t>
         </is>
       </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>_3069@_3053</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -3073,6 +3299,11 @@
           <t>All</t>
         </is>
       </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>_3070@_3053</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -3130,6 +3361,11 @@
           <t>All</t>
         </is>
       </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>_3071@_3053</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -3187,6 +3423,11 @@
           <t>All</t>
         </is>
       </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>_3072@_3053</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -3244,6 +3485,11 @@
           <t>All</t>
         </is>
       </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>_3073@_3053</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -3301,6 +3547,11 @@
           <t>Unlocked_0x11</t>
         </is>
       </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>_3074@_3053</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -3358,6 +3609,11 @@
           <t>Locked, Unlocked_0x1</t>
         </is>
       </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>_3075@_3053</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -3415,6 +3671,11 @@
           <t>Unlocked_0x1</t>
         </is>
       </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>_3076@_3053</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -3472,6 +3733,11 @@
           <t>Locked, Unlocked_0x1</t>
         </is>
       </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>_3077@_3053</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -3529,6 +3795,11 @@
           <t>All</t>
         </is>
       </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>_3078@_3053</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -3586,6 +3857,11 @@
           <t>All</t>
         </is>
       </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>_3079@_3053</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -3643,6 +3919,11 @@
           <t>All</t>
         </is>
       </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>_3080@_3053</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -3700,6 +3981,11 @@
           <t>All</t>
         </is>
       </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>_3081@_3053</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -3757,6 +4043,11 @@
           <t>All</t>
         </is>
       </c>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>_3082@_3053</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -3814,6 +4105,11 @@
           <t>Locked, Unlocked_0x1</t>
         </is>
       </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>_3083@_3053</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -3871,6 +4167,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>_3084@_3053</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -3928,6 +4229,11 @@
           <t>Unlocked_0x1</t>
         </is>
       </c>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>_3085@_3053</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -3985,6 +4291,11 @@
           <t>All</t>
         </is>
       </c>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>_3086@_3053</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -4042,6 +4353,11 @@
           <t>Locked, Unlocked_0x1</t>
         </is>
       </c>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>_3087@_3053</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -4099,6 +4415,11 @@
           <t>Locked, Unlocked_0x1</t>
         </is>
       </c>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>_3088@_3053</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -4156,6 +4477,11 @@
           <t>Locked, Unlocked_0x1</t>
         </is>
       </c>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>_3089@_3053</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -4213,6 +4539,11 @@
           <t>Locked, Unlocked_0x1</t>
         </is>
       </c>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>_3090@_3053</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -4270,6 +4601,11 @@
           <t>Locked, Unlocked_0x1</t>
         </is>
       </c>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>_3091@_3053</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -4327,6 +4663,11 @@
           <t>Locked, Unlocked_0x1</t>
         </is>
       </c>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>_3092@_3053</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -4384,6 +4725,11 @@
           <t>All</t>
         </is>
       </c>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>_3094@_3053</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -4441,6 +4787,11 @@
           <t>Locked, Unlocked_0x1</t>
         </is>
       </c>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>_3095@_3053</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -4498,6 +4849,11 @@
           <t>All</t>
         </is>
       </c>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>_3096@_3053</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -4555,6 +4911,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>_3097@_3053</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -4612,6 +4973,11 @@
           <t>Locked, Unlocked_0x1</t>
         </is>
       </c>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>_3098@_3053</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -4669,6 +5035,11 @@
           <t>Locked, Unlocked_0x1</t>
         </is>
       </c>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>_3099@_3053</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -4726,6 +5097,11 @@
           <t>Locked, Unlocked_0x1</t>
         </is>
       </c>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>_3100@_3053</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -4783,6 +5159,11 @@
           <t>Locked, Unlocked_0x1</t>
         </is>
       </c>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>_3101@_3053</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -4840,6 +5221,11 @@
           <t>Locked, Unlocked_0x1</t>
         </is>
       </c>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>_3102@_3053</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -4897,6 +5283,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>_3105@_3053</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -4954,6 +5345,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>_3106@_3053</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -5011,6 +5407,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>_3107@_3053</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -5068,6 +5469,11 @@
           <t>Locked, Unlocked_0x1</t>
         </is>
       </c>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>_3108@_3053</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -5125,6 +5531,11 @@
           <t>Unlocked_0x1</t>
         </is>
       </c>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>_3109@_3053</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -5182,6 +5593,11 @@
           <t>Unlocked_0x1</t>
         </is>
       </c>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>_3110@_3053</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -5239,6 +5655,11 @@
           <t>Locked</t>
         </is>
       </c>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>_3113@_3053</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -5296,6 +5717,11 @@
           <t>Unlocked_0x1</t>
         </is>
       </c>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>_3115@_3053</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -5353,6 +5779,11 @@
           <t>Unlocked_0x1</t>
         </is>
       </c>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>_3116@_3053</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -5410,6 +5841,11 @@
           <t>Unlocked_0x1</t>
         </is>
       </c>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>_3117@_3053</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -5467,6 +5903,11 @@
           <t>Unlocked_0x11, Unlocked_0x1</t>
         </is>
       </c>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>_3119@_3053</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -5524,6 +5965,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>_3120@_3053</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -5581,6 +6027,11 @@
           <t>Locked, Unlocked_0x1</t>
         </is>
       </c>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>_3122@_3053</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -5638,6 +6089,11 @@
           <t>Locked, Unlocked_0x1</t>
         </is>
       </c>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>_3123@_3053</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -5695,6 +6151,11 @@
           <t>Locked, Unlocked_0x1</t>
         </is>
       </c>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>_3124@_3053</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -5752,6 +6213,11 @@
           <t>Locked, Unlocked_0x1</t>
         </is>
       </c>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>_3125@_3053</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -5809,6 +6275,11 @@
           <t>Locked, Unlocked_0x1</t>
         </is>
       </c>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>_3126@_3053</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -5866,6 +6337,11 @@
           <t>All</t>
         </is>
       </c>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>_3004@_3159</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -5923,6 +6399,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>_3164@_3159</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -5980,6 +6461,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>_3166@_3159</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -6037,6 +6523,11 @@
           <t>All</t>
         </is>
       </c>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>_3009@_3159</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -6094,6 +6585,11 @@
           <t>All</t>
         </is>
       </c>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>_3010@_3159</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -6151,6 +6647,11 @@
           <t>All</t>
         </is>
       </c>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>_3011@_3159</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -6208,6 +6709,11 @@
           <t>All</t>
         </is>
       </c>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>_3012@_3159</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -6265,6 +6771,11 @@
           <t>All</t>
         </is>
       </c>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>_3013@_3159</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -6322,6 +6833,11 @@
           <t>All</t>
         </is>
       </c>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>_3014@_3159</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -6379,6 +6895,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>_3169@_3159</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
@@ -6436,6 +6957,11 @@
           <t>Locked, Unlocked_0x1</t>
         </is>
       </c>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>_3021@_3159</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -6493,6 +7019,11 @@
           <t>Locked, Unlocked_0x1</t>
         </is>
       </c>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t>_3022@_3159</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
@@ -6550,6 +7081,11 @@
           <t>All</t>
         </is>
       </c>
+      <c r="L107" s="2" t="inlineStr">
+        <is>
+          <t>_3172@_3159</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -6607,6 +7143,11 @@
           <t>All</t>
         </is>
       </c>
+      <c r="L108" s="2" t="inlineStr">
+        <is>
+          <t>_3173@_3159</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
@@ -6664,6 +7205,11 @@
           <t>All</t>
         </is>
       </c>
+      <c r="L109" s="2" t="inlineStr">
+        <is>
+          <t>_3174@_3159</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -6721,6 +7267,11 @@
           <t>All</t>
         </is>
       </c>
+      <c r="L110" s="2" t="inlineStr">
+        <is>
+          <t>_3175@_3159</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -6778,6 +7329,11 @@
           <t>All</t>
         </is>
       </c>
+      <c r="L111" s="2" t="inlineStr">
+        <is>
+          <t>_3176@_3159</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -6835,6 +7391,11 @@
           <t>All</t>
         </is>
       </c>
+      <c r="L112" s="2" t="inlineStr">
+        <is>
+          <t>_3177@_3159</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -6892,6 +7453,11 @@
           <t>All</t>
         </is>
       </c>
+      <c r="L113" s="2" t="inlineStr">
+        <is>
+          <t>_3179@_3159</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -6949,6 +7515,11 @@
           <t>All</t>
         </is>
       </c>
+      <c r="L114" s="2" t="inlineStr">
+        <is>
+          <t>_3181@_3159</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -7006,6 +7577,11 @@
           <t>All</t>
         </is>
       </c>
+      <c r="L115" s="2" t="inlineStr">
+        <is>
+          <t>_3183@_3159</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -7063,6 +7639,11 @@
           <t>Locked, Unlocked_0x11</t>
         </is>
       </c>
+      <c r="L116" s="2" t="inlineStr">
+        <is>
+          <t>_3187@_3159</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -7120,6 +7701,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="L117" s="2" t="inlineStr">
+        <is>
+          <t>_3189@_3159</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -7177,6 +7763,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="L118" s="2" t="inlineStr">
+        <is>
+          <t>_3191@_3159</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
@@ -7234,6 +7825,11 @@
           <t>Unlocked_0x11</t>
         </is>
       </c>
+      <c r="L119" s="2" t="inlineStr">
+        <is>
+          <t>_3193@_3159</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -7291,6 +7887,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="L120" s="2" t="inlineStr">
+        <is>
+          <t>_3195@_3159</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
@@ -7348,6 +7949,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="L121" s="2" t="inlineStr">
+        <is>
+          <t>_3197@_3159</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
@@ -7405,6 +8011,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="L122" s="2" t="inlineStr">
+        <is>
+          <t>_3199@_3159</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
@@ -7462,6 +8073,11 @@
           <t>Locked</t>
         </is>
       </c>
+      <c r="L123" s="2" t="inlineStr">
+        <is>
+          <t>_3201@_3159</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
@@ -7519,6 +8135,11 @@
           <t>Unlocked_0x11, Unlocked_0x1</t>
         </is>
       </c>
+      <c r="L124" s="2" t="inlineStr">
+        <is>
+          <t>_3203@_3159</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
@@ -7576,6 +8197,11 @@
           <t>Unlocked_0x11, Unlocked_0x1</t>
         </is>
       </c>
+      <c r="L125" s="2" t="inlineStr">
+        <is>
+          <t>_3204@_3159</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
@@ -7633,6 +8259,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="L126" s="2" t="inlineStr">
+        <is>
+          <t>_3206@_3159</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
@@ -7690,6 +8321,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="L127" s="2" t="inlineStr">
+        <is>
+          <t>_3207@_3159</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
@@ -7747,6 +8383,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="L128" s="2" t="inlineStr">
+        <is>
+          <t>_3208@_3159</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
@@ -7804,6 +8445,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="L129" s="2" t="inlineStr">
+        <is>
+          <t>_3209@_3159</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -7861,6 +8507,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="L130" s="2" t="inlineStr">
+        <is>
+          <t>_3210@_3159</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
@@ -7918,6 +8569,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="L131" s="2" t="inlineStr">
+        <is>
+          <t>_3211@_3159</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
@@ -7975,6 +8631,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="L132" s="2" t="inlineStr">
+        <is>
+          <t>_3212@_3159</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
@@ -8032,6 +8693,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="L133" s="2" t="inlineStr">
+        <is>
+          <t>_3213@_3159</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
@@ -8089,6 +8755,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="L134" s="2" t="inlineStr">
+        <is>
+          <t>_3214@_3159</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
@@ -8146,6 +8817,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="L135" s="2" t="inlineStr">
+        <is>
+          <t>_3215@_3159</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
@@ -8203,6 +8879,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="L136" s="2" t="inlineStr">
+        <is>
+          <t>_3216@_3159</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
@@ -8260,6 +8941,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="L137" s="2" t="inlineStr">
+        <is>
+          <t>_3217@_3159</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
@@ -8317,6 +9003,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="L138" s="2" t="inlineStr">
+        <is>
+          <t>_3218@_3159</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
@@ -8374,6 +9065,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="L139" s="2" t="inlineStr">
+        <is>
+          <t>_3219@_3159</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
@@ -8431,9 +9127,14 @@
           <t>-</t>
         </is>
       </c>
+      <c r="L140" s="2" t="inlineStr">
+        <is>
+          <t>_3220@_3159</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K140"/>
+  <autoFilter ref="A1:L140"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8444,7 +9145,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y100"/>
+  <dimension ref="A1:AA100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -8472,6 +9173,8 @@
     <col width="12" customWidth="1" min="23" max="23"/>
     <col width="27" customWidth="1" min="24" max="24"/>
     <col width="16" customWidth="1" min="25" max="25"/>
+    <col width="10" customWidth="1" min="26" max="26"/>
+    <col width="13" customWidth="1" min="27" max="27"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8598,6 +9301,16 @@
       <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Write Security</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>DID Ref</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Element Ref</t>
         </is>
       </c>
     </row>
@@ -8703,6 +9416,16 @@
           <t>Unlocked_0x1</t>
         </is>
       </c>
+      <c r="Z2" s="2" t="inlineStr">
+        <is>
+          <t>_1142</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
+          <t>_1142:0</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -8798,6 +9521,16 @@
       </c>
       <c r="X3" s="2" t="inlineStr"/>
       <c r="Y3" s="2" t="inlineStr"/>
+      <c r="Z3" s="2" t="inlineStr">
+        <is>
+          <t>_1143</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
+          <t>_1143:0</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -8898,6 +9631,16 @@
       </c>
       <c r="X4" s="2" t="inlineStr"/>
       <c r="Y4" s="2" t="inlineStr"/>
+      <c r="Z4" s="2" t="inlineStr">
+        <is>
+          <t>_1144</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
+          <t>_1144:0</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -9001,6 +9744,16 @@
       </c>
       <c r="X5" s="2" t="inlineStr"/>
       <c r="Y5" s="2" t="inlineStr"/>
+      <c r="Z5" s="2" t="inlineStr">
+        <is>
+          <t>_1145</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
+          <t>_1145:0</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -9103,6 +9856,16 @@
       </c>
       <c r="X6" s="2" t="inlineStr"/>
       <c r="Y6" s="2" t="inlineStr"/>
+      <c r="Z6" s="2" t="inlineStr">
+        <is>
+          <t>_1146</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
+          <t>_1146:0</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -9198,6 +9961,16 @@
       </c>
       <c r="X7" s="2" t="inlineStr"/>
       <c r="Y7" s="2" t="inlineStr"/>
+      <c r="Z7" s="2" t="inlineStr">
+        <is>
+          <t>_1146</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
+          <t>_1146:1</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -9298,6 +10071,16 @@
       </c>
       <c r="X8" s="2" t="inlineStr"/>
       <c r="Y8" s="2" t="inlineStr"/>
+      <c r="Z8" s="2" t="inlineStr">
+        <is>
+          <t>_1147</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
+          <t>_1147:0</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -9412,6 +10195,16 @@
       </c>
       <c r="X9" s="2" t="inlineStr"/>
       <c r="Y9" s="2" t="inlineStr"/>
+      <c r="Z9" s="2" t="inlineStr">
+        <is>
+          <t>_1148</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
+          <t>_1148:0</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -9515,6 +10308,16 @@
       </c>
       <c r="X10" s="2" t="inlineStr"/>
       <c r="Y10" s="2" t="inlineStr"/>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t>_1149</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
+          <t>_1149:0</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -9618,6 +10421,16 @@
       </c>
       <c r="X11" s="2" t="inlineStr"/>
       <c r="Y11" s="2" t="inlineStr"/>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>_1149</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>_1149:1</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -9719,6 +10532,16 @@
       </c>
       <c r="X12" s="2" t="inlineStr"/>
       <c r="Y12" s="2" t="inlineStr"/>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>_1149</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>_1149:2</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -9822,6 +10645,16 @@
       </c>
       <c r="X13" s="2" t="inlineStr"/>
       <c r="Y13" s="2" t="inlineStr"/>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>_1149</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>_1149:3</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -9925,6 +10758,16 @@
       </c>
       <c r="X14" s="2" t="inlineStr"/>
       <c r="Y14" s="2" t="inlineStr"/>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>_1149</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>_1149:4</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -10028,6 +10871,16 @@
       </c>
       <c r="X15" s="2" t="inlineStr"/>
       <c r="Y15" s="2" t="inlineStr"/>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>_1149</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>_1149:5</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -10127,6 +10980,16 @@
       </c>
       <c r="X16" s="2" t="inlineStr"/>
       <c r="Y16" s="2" t="inlineStr"/>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>_1149</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>_1149:6</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -10226,6 +11089,16 @@
       </c>
       <c r="X17" s="2" t="inlineStr"/>
       <c r="Y17" s="2" t="inlineStr"/>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>_1149</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>_1149:7</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -10325,6 +11198,16 @@
       </c>
       <c r="X18" s="2" t="inlineStr"/>
       <c r="Y18" s="2" t="inlineStr"/>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>_1149</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>_1149:8</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -10424,6 +11307,16 @@
       </c>
       <c r="X19" s="2" t="inlineStr"/>
       <c r="Y19" s="2" t="inlineStr"/>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>_1149</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>_1149:9</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -10527,6 +11420,16 @@
       </c>
       <c r="X20" s="2" t="inlineStr"/>
       <c r="Y20" s="2" t="inlineStr"/>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>_1149</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>_1149:10</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -10630,6 +11533,16 @@
       </c>
       <c r="X21" s="2" t="inlineStr"/>
       <c r="Y21" s="2" t="inlineStr"/>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>_1149</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>_1149:11</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -10733,6 +11646,16 @@
       </c>
       <c r="X22" s="2" t="inlineStr"/>
       <c r="Y22" s="2" t="inlineStr"/>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>_1149</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>_1149:12</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -10828,6 +11751,16 @@
       </c>
       <c r="X23" s="2" t="inlineStr"/>
       <c r="Y23" s="2" t="inlineStr"/>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>_1149</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>_1149:13</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -10927,6 +11860,16 @@
       </c>
       <c r="X24" s="2" t="inlineStr"/>
       <c r="Y24" s="2" t="inlineStr"/>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>_1150</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>_1150:0</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -11026,6 +11969,16 @@
       </c>
       <c r="X25" s="2" t="inlineStr"/>
       <c r="Y25" s="2" t="inlineStr"/>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>_1150</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>_1150:1</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -11125,6 +12078,16 @@
       </c>
       <c r="X26" s="2" t="inlineStr"/>
       <c r="Y26" s="2" t="inlineStr"/>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>_1150</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>_1150:2</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -11228,6 +12191,16 @@
       </c>
       <c r="X27" s="2" t="inlineStr"/>
       <c r="Y27" s="2" t="inlineStr"/>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>_1150</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>_1150:3</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -11331,6 +12304,16 @@
       </c>
       <c r="X28" s="2" t="inlineStr"/>
       <c r="Y28" s="2" t="inlineStr"/>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>_1150</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>_1150:4</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -11434,6 +12417,16 @@
       </c>
       <c r="X29" s="2" t="inlineStr"/>
       <c r="Y29" s="2" t="inlineStr"/>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>_1150</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>_1150:5</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -11537,6 +12530,16 @@
       </c>
       <c r="X30" s="2" t="inlineStr"/>
       <c r="Y30" s="2" t="inlineStr"/>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>_1151</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>_1151:0</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -11640,6 +12643,16 @@
       </c>
       <c r="X31" s="2" t="inlineStr"/>
       <c r="Y31" s="2" t="inlineStr"/>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>_1152</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>_1152:0</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -11743,6 +12756,16 @@
       </c>
       <c r="X32" s="2" t="inlineStr"/>
       <c r="Y32" s="2" t="inlineStr"/>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>_1153</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>_1153:0</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -11838,6 +12861,16 @@
       </c>
       <c r="X33" s="2" t="inlineStr"/>
       <c r="Y33" s="2" t="inlineStr"/>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>_1154</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>_1154:0</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -11933,6 +12966,16 @@
       </c>
       <c r="X34" s="2" t="inlineStr"/>
       <c r="Y34" s="2" t="inlineStr"/>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>_1155</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>_1155:0</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -12028,6 +13071,16 @@
           <t>All</t>
         </is>
       </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>_1156</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>_1156:0</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -12123,6 +13176,16 @@
       </c>
       <c r="X36" s="2" t="inlineStr"/>
       <c r="Y36" s="2" t="inlineStr"/>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>_1157</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>_1157:0</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -12218,6 +13281,16 @@
       </c>
       <c r="X37" s="2" t="inlineStr"/>
       <c r="Y37" s="2" t="inlineStr"/>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>_1158</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>_1158:0</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -12313,6 +13386,16 @@
       </c>
       <c r="X38" s="2" t="inlineStr"/>
       <c r="Y38" s="2" t="inlineStr"/>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>_1159</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>_1159:0</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -12408,6 +13491,16 @@
       </c>
       <c r="X39" s="2" t="inlineStr"/>
       <c r="Y39" s="2" t="inlineStr"/>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>_1160</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>_1160:0</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -12503,6 +13596,16 @@
       </c>
       <c r="X40" s="2" t="inlineStr"/>
       <c r="Y40" s="2" t="inlineStr"/>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>_1160</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>_1160:1</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -12598,6 +13701,16 @@
       </c>
       <c r="X41" s="2" t="inlineStr"/>
       <c r="Y41" s="2" t="inlineStr"/>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>_1160</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>_1160:2</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -12693,6 +13806,16 @@
       </c>
       <c r="X42" s="2" t="inlineStr"/>
       <c r="Y42" s="2" t="inlineStr"/>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>_1160</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>_1160:3</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -12788,6 +13911,16 @@
       </c>
       <c r="X43" s="2" t="inlineStr"/>
       <c r="Y43" s="2" t="inlineStr"/>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>_1160</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>_1160:4</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -12883,6 +14016,16 @@
       </c>
       <c r="X44" s="2" t="inlineStr"/>
       <c r="Y44" s="2" t="inlineStr"/>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>_1160</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>_1160:5</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -12978,6 +14121,16 @@
       </c>
       <c r="X45" s="2" t="inlineStr"/>
       <c r="Y45" s="2" t="inlineStr"/>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>_1160</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>_1160:6</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -13073,6 +14226,16 @@
       </c>
       <c r="X46" s="2" t="inlineStr"/>
       <c r="Y46" s="2" t="inlineStr"/>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>_1160</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>_1160:7</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -13168,6 +14331,16 @@
       </c>
       <c r="X47" s="2" t="inlineStr"/>
       <c r="Y47" s="2" t="inlineStr"/>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>_1160</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>_1160:8</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -13263,6 +14436,16 @@
       </c>
       <c r="X48" s="2" t="inlineStr"/>
       <c r="Y48" s="2" t="inlineStr"/>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>_1160</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>_1160:9</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -13358,6 +14541,16 @@
       </c>
       <c r="X49" s="2" t="inlineStr"/>
       <c r="Y49" s="2" t="inlineStr"/>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>_1160</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>_1160:10</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -13453,6 +14646,16 @@
       </c>
       <c r="X50" s="2" t="inlineStr"/>
       <c r="Y50" s="2" t="inlineStr"/>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>_1160</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>_1160:11</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -13548,6 +14751,16 @@
       </c>
       <c r="X51" s="2" t="inlineStr"/>
       <c r="Y51" s="2" t="inlineStr"/>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>_1160</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>_1160:12</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -13643,6 +14856,16 @@
       </c>
       <c r="X52" s="2" t="inlineStr"/>
       <c r="Y52" s="2" t="inlineStr"/>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>_1160</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>_1160:13</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -13738,6 +14961,16 @@
       </c>
       <c r="X53" s="2" t="inlineStr"/>
       <c r="Y53" s="2" t="inlineStr"/>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>_1160</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>_1160:14</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -13833,6 +15066,16 @@
       </c>
       <c r="X54" s="2" t="inlineStr"/>
       <c r="Y54" s="2" t="inlineStr"/>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>_1160</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>_1160:15</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -13928,6 +15171,16 @@
       </c>
       <c r="X55" s="2" t="inlineStr"/>
       <c r="Y55" s="2" t="inlineStr"/>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>_1160</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>_1160:16</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -14023,6 +15276,16 @@
       </c>
       <c r="X56" s="2" t="inlineStr"/>
       <c r="Y56" s="2" t="inlineStr"/>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>_1160</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>_1160:17</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -14118,6 +15381,16 @@
       </c>
       <c r="X57" s="2" t="inlineStr"/>
       <c r="Y57" s="2" t="inlineStr"/>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>_1160</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>_1160:18</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -14213,6 +15486,16 @@
       </c>
       <c r="X58" s="2" t="inlineStr"/>
       <c r="Y58" s="2" t="inlineStr"/>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>_1160</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>_1160:19</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -14308,6 +15591,16 @@
       </c>
       <c r="X59" s="2" t="inlineStr"/>
       <c r="Y59" s="2" t="inlineStr"/>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>_1160</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>_1160:20</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -14403,6 +15696,16 @@
       </c>
       <c r="X60" s="2" t="inlineStr"/>
       <c r="Y60" s="2" t="inlineStr"/>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>_1160</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>_1160:21</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -14498,6 +15801,16 @@
       </c>
       <c r="X61" s="2" t="inlineStr"/>
       <c r="Y61" s="2" t="inlineStr"/>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>_1160</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>_1160:22</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -14598,6 +15911,16 @@
       </c>
       <c r="X62" s="2" t="inlineStr"/>
       <c r="Y62" s="2" t="inlineStr"/>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>_1161</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>_1161:0</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -14697,6 +16020,16 @@
       </c>
       <c r="X63" s="2" t="inlineStr"/>
       <c r="Y63" s="2" t="inlineStr"/>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>_1162</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>_1162:0</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -14796,6 +16129,16 @@
       </c>
       <c r="X64" s="2" t="inlineStr"/>
       <c r="Y64" s="2" t="inlineStr"/>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>_1163</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>_1163:0</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -14891,6 +16234,16 @@
       </c>
       <c r="X65" s="2" t="inlineStr"/>
       <c r="Y65" s="2" t="inlineStr"/>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>_1164</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>_1164:0</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -14986,6 +16339,16 @@
       </c>
       <c r="X66" s="2" t="inlineStr"/>
       <c r="Y66" s="2" t="inlineStr"/>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>_1164</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>_1164:1</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -15081,6 +16444,16 @@
       </c>
       <c r="X67" s="2" t="inlineStr"/>
       <c r="Y67" s="2" t="inlineStr"/>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>_1165</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>_1165:0</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -15176,6 +16549,16 @@
       </c>
       <c r="X68" s="2" t="inlineStr"/>
       <c r="Y68" s="2" t="inlineStr"/>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>_1165</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>_1165:1</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -15271,6 +16654,16 @@
       </c>
       <c r="X69" s="2" t="inlineStr"/>
       <c r="Y69" s="2" t="inlineStr"/>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>_1165</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>_1165:2</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -15366,6 +16759,16 @@
       </c>
       <c r="X70" s="2" t="inlineStr"/>
       <c r="Y70" s="2" t="inlineStr"/>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>_1165</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>_1165:3</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -15467,6 +16870,16 @@
       </c>
       <c r="X71" s="2" t="inlineStr"/>
       <c r="Y71" s="2" t="inlineStr"/>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>_1166</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>_1166:0</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -15562,6 +16975,16 @@
       </c>
       <c r="X72" s="2" t="inlineStr"/>
       <c r="Y72" s="2" t="inlineStr"/>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>_1167</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>_1167:0</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -15657,6 +17080,16 @@
       </c>
       <c r="X73" s="2" t="inlineStr"/>
       <c r="Y73" s="2" t="inlineStr"/>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>_1167</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>_1167:1</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -15752,6 +17185,16 @@
       </c>
       <c r="X74" s="2" t="inlineStr"/>
       <c r="Y74" s="2" t="inlineStr"/>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>_1167</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>_1167:2</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -15847,6 +17290,16 @@
       </c>
       <c r="X75" s="2" t="inlineStr"/>
       <c r="Y75" s="2" t="inlineStr"/>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>_1167</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>_1167:3</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -15942,6 +17395,16 @@
       </c>
       <c r="X76" s="2" t="inlineStr"/>
       <c r="Y76" s="2" t="inlineStr"/>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>_1167</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>_1167:4</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -16037,6 +17500,16 @@
       </c>
       <c r="X77" s="2" t="inlineStr"/>
       <c r="Y77" s="2" t="inlineStr"/>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>_1168</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>_1168:0</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -16132,6 +17605,16 @@
       </c>
       <c r="X78" s="2" t="inlineStr"/>
       <c r="Y78" s="2" t="inlineStr"/>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>_1168</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>_1168:1</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -16227,6 +17710,16 @@
       </c>
       <c r="X79" s="2" t="inlineStr"/>
       <c r="Y79" s="2" t="inlineStr"/>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>_1168</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>_1168:2</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -16322,6 +17815,16 @@
       </c>
       <c r="X80" s="2" t="inlineStr"/>
       <c r="Y80" s="2" t="inlineStr"/>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>_1168</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>_1168:3</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -16417,6 +17920,16 @@
       </c>
       <c r="X81" s="2" t="inlineStr"/>
       <c r="Y81" s="2" t="inlineStr"/>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>_1168</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>_1168:4</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -16512,6 +18025,16 @@
       </c>
       <c r="X82" s="2" t="inlineStr"/>
       <c r="Y82" s="2" t="inlineStr"/>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>_1169</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>_1169:0</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -16607,6 +18130,16 @@
       </c>
       <c r="X83" s="2" t="inlineStr"/>
       <c r="Y83" s="2" t="inlineStr"/>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>_1170</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>_1170:0</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -16714,6 +18247,16 @@
           <t>Unlocked_0x11</t>
         </is>
       </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>_1171</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>_1171:0</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -16821,6 +18364,16 @@
           <t>Unlocked_0x11</t>
         </is>
       </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>_1171</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>_1171:1</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -16926,6 +18479,16 @@
       <c r="Y86" s="2" t="inlineStr">
         <is>
           <t>Unlocked_0x11</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>_1171</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>_1171:2</t>
         </is>
       </c>
     </row>
@@ -17031,6 +18594,16 @@
           <t>Unlocked_0x11</t>
         </is>
       </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>_1171</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>_1171:3</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -17126,6 +18699,16 @@
       </c>
       <c r="X88" s="2" t="inlineStr"/>
       <c r="Y88" s="2" t="inlineStr"/>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>_1172</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>_1172:0</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -17221,6 +18804,16 @@
       </c>
       <c r="X89" s="2" t="inlineStr"/>
       <c r="Y89" s="2" t="inlineStr"/>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>_1173</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>_1173:0</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -17316,6 +18909,16 @@
       </c>
       <c r="X90" s="2" t="inlineStr"/>
       <c r="Y90" s="2" t="inlineStr"/>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>_1174</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>_1174:0</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -17411,6 +19014,16 @@
       </c>
       <c r="X91" s="2" t="inlineStr"/>
       <c r="Y91" s="2" t="inlineStr"/>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>_1175</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>_1175:0</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -17506,6 +19119,16 @@
       </c>
       <c r="X92" s="2" t="inlineStr"/>
       <c r="Y92" s="2" t="inlineStr"/>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>_1176</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>_1176:0</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -17601,6 +19224,16 @@
       </c>
       <c r="X93" s="2" t="inlineStr"/>
       <c r="Y93" s="2" t="inlineStr"/>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>_1177</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>_1177:0</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -17696,6 +19329,16 @@
       </c>
       <c r="X94" s="2" t="inlineStr"/>
       <c r="Y94" s="2" t="inlineStr"/>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>_1178</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>_1178:0</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -17791,6 +19434,16 @@
       </c>
       <c r="X95" s="2" t="inlineStr"/>
       <c r="Y95" s="2" t="inlineStr"/>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>_1179</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>_1179:0</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -17894,6 +19547,16 @@
           <t>Unlocked_0x1</t>
         </is>
       </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>_1180</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>_1180:0</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -17989,6 +19652,16 @@
       </c>
       <c r="X97" s="2" t="inlineStr"/>
       <c r="Y97" s="2" t="inlineStr"/>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>_1181</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>_1181:0</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -18084,6 +19757,16 @@
       </c>
       <c r="X98" s="2" t="inlineStr"/>
       <c r="Y98" s="2" t="inlineStr"/>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>_1182</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>_1182:0</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -18179,6 +19862,16 @@
       </c>
       <c r="X99" s="2" t="inlineStr"/>
       <c r="Y99" s="2" t="inlineStr"/>
+      <c r="Z99" s="2" t="inlineStr">
+        <is>
+          <t>_1183</t>
+        </is>
+      </c>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>_1183:0</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -18274,9 +19967,19 @@
       </c>
       <c r="X100" s="2" t="inlineStr"/>
       <c r="Y100" s="2" t="inlineStr"/>
+      <c r="Z100" s="2" t="inlineStr">
+        <is>
+          <t>_1184</t>
+        </is>
+      </c>
+      <c r="AA100" s="2" t="inlineStr">
+        <is>
+          <t>_1184:0</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Y100"/>
+  <autoFilter ref="A1:AA100"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -18287,7 +19990,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB34"/>
+  <dimension ref="A1:AC34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -18318,6 +20021,7 @@
     <col width="48" customWidth="1" min="26" max="26"/>
     <col width="40" customWidth="1" min="27" max="27"/>
     <col width="41" customWidth="1" min="28" max="28"/>
+    <col width="10" customWidth="1" min="29" max="29"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -18459,6 +20163,11 @@
       <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>DS_DTCExistingExtendedDataRecordNumbers</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>CDD Ref</t>
         </is>
       </c>
     </row>
@@ -18620,6 +20329,11 @@
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AC2" s="2" t="inlineStr">
+        <is>
+          <t>_2986</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -18752,6 +20466,11 @@
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AC3" s="2" t="inlineStr">
+        <is>
+          <t>_2987</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -18892,6 +20611,11 @@
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
+      <c r="AC4" s="2" t="inlineStr">
+        <is>
+          <t>_2988</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -19030,6 +20754,11 @@
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
+      <c r="AC5" s="2" t="inlineStr">
+        <is>
+          <t>_2989</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -19166,6 +20895,11 @@
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr">
+        <is>
+          <t>_2990</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -19298,6 +21032,11 @@
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr">
+        <is>
+          <t>_2991</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -19447,6 +21186,11 @@
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr">
+        <is>
+          <t>_2992</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -19577,6 +21321,11 @@
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AC9" s="2" t="inlineStr">
+        <is>
+          <t>_3128</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -19703,6 +21452,11 @@
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>_3129</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -19837,6 +21591,11 @@
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>_3130</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -19961,6 +21720,11 @@
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>_3131</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -20113,6 +21877,11 @@
           <t>tbd</t>
         </is>
       </c>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>_3132</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -20237,6 +22006,11 @@
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>_3133</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -20367,6 +22141,11 @@
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>_3134</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -20499,6 +22278,11 @@
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>_3135</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -20636,6 +22420,11 @@
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>_3136</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -20773,6 +22562,11 @@
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>_3137</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -20909,6 +22703,11 @@
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>_3138</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -21046,6 +22845,11 @@
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>_3139</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -21182,6 +22986,11 @@
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>_3140</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -21318,6 +23127,11 @@
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>_3141</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -21485,6 +23299,11 @@
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr"/>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>_3142</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -21625,6 +23444,11 @@
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>_3143</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -21771,6 +23595,11 @@
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr"/>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>_3144</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -21915,6 +23744,11 @@
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr"/>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>_3145</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -22045,6 +23879,11 @@
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr"/>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>_3146</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -22196,6 +24035,11 @@
           <t>tbd</t>
         </is>
       </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>_3147</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -22347,6 +24191,11 @@
           <t>tbd</t>
         </is>
       </c>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>_3148</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -22484,6 +24333,11 @@
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr"/>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>_3149</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -22606,6 +24460,11 @@
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr"/>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>_3150</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -22746,6 +24605,11 @@
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr"/>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>_3151</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -22904,6 +24768,11 @@
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr"/>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>_3152</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -23060,9 +24929,14 @@
           <t>tbd</t>
         </is>
       </c>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>_3153</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AB34"/>
+  <autoFilter ref="A1:AC34"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -23073,7 +24947,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -23086,6 +24960,7 @@
     <col width="29" customWidth="1" min="8" max="8"/>
     <col width="60" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -23139,6 +25014,11 @@
           <t>Description</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>CDD Ref</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -23192,6 +25072,11 @@
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>_3028@_2995</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -23245,6 +25130,11 @@
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>_3032@_2995</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -23295,6 +25185,11 @@
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>_3036@_2995</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -23345,6 +25240,11 @@
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>_3040@_2995</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -23396,6 +25296,11 @@
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>_3044@_2995</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -23446,6 +25351,11 @@
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>_3048@_2995</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -23494,6 +25404,11 @@
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>_3112@_3053</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -23547,6 +25462,11 @@
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>_3114@_3053</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -23597,6 +25517,11 @@
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>_3118@_3053</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -23641,6 +25566,11 @@
       </c>
       <c r="I11" s="2" t="inlineStr"/>
       <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>_3186@_3159</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -23685,6 +25615,11 @@
       </c>
       <c r="I12" s="2" t="inlineStr"/>
       <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>_3188@_3159</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -23729,6 +25664,11 @@
       </c>
       <c r="I13" s="2" t="inlineStr"/>
       <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>_3190@_3159</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -23777,6 +25717,11 @@
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>_3192@_3159</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -23821,6 +25766,11 @@
       </c>
       <c r="I15" s="2" t="inlineStr"/>
       <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>_3194@_3159</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -23865,6 +25815,11 @@
       </c>
       <c r="I16" s="2" t="inlineStr"/>
       <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>_3196@_3159</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -23909,6 +25864,11 @@
       </c>
       <c r="I17" s="2" t="inlineStr"/>
       <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>_3198@_3159</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -23957,6 +25917,11 @@
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>_3200@_3159</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -24007,9 +25972,14 @@
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>_3202@_3159</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J19"/>
+  <autoFilter ref="A1:K19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Cdd Parsing/RADAR_G7_CHERY03_APP_and_BOOT.xlsx
+++ b/Cdd Parsing/RADAR_G7_CHERY03_APP_and_BOOT.xlsx
@@ -709,37 +709,37 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>3E</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3E 00</t>
+          <t>11 01</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Tester Present</t>
+          <t>Reset</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Tester Present</t>
+          <t>Hard Reset</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Send</t>
+          <t>Reset</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>TesterPresent_Send</t>
+          <t>Hard_Reset_Reset</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>($3E) TesterPresent</t>
+          <t>($11) EcuReset</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -749,17 +749,17 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>DefaultSession, ProgrammingSession, ExtendedDiagnosticSession</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Locked, Unlocked_0x11, Unlocked_0x1</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>_3004@_2995</t>
+          <t>_3007@_2995</t>
         </is>
       </c>
     </row>
@@ -771,37 +771,37 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>11 01</t>
+          <t>28 00</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Reset</t>
+          <t>Communication Control</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Hard Reset</t>
+          <t>EnableRxAndEnableTx</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Reset</t>
+          <t>Control</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Hard_Reset_Reset</t>
+          <t>EnableRxAndEnableTx_Control</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>($11) EcuReset</t>
+          <t>($28) CommunicationControl</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -811,17 +811,17 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>DefaultSession, ProgrammingSession, ExtendedDiagnosticSession</t>
+          <t>ExtendedDiagnosticSession</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>Locked, Unlocked_0x11, Unlocked_0x1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>_3007@_2995</t>
+          <t>_3017@_2995</t>
         </is>
       </c>
     </row>
@@ -833,57 +833,57 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>29 01 00</t>
+          <t>28 01</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Authentication</t>
+          <t>Communication Control</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Authentication</t>
+          <t>EnableRxAndDisableTx</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Verify Certificate Unidirectional</t>
+          <t>Control</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Authentication_Verify_Certificate_Unidirectional</t>
+          <t>EnableRxAndDisableTx_Control</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>($29) Authentication - VerifyCertificateUnidirectional</t>
+          <t>($28) CommunicationControl</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Physical, Functional</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>ExtendedDiagnosticSession</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>_3009@_2995</t>
+          <t>_3019@_2995</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>29 02 00</t>
+          <t>29 00</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -915,17 +915,17 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Verify Certificate Bidirectional</t>
+          <t>Deauthentication</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Authentication_Verify_Certificate_Bidirectional</t>
+          <t>Authentication_Deauthentication</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>($29) Authentication - VerifyCertificateBidirectional</t>
+          <t>($29) Authentication - DeAuthentication</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>_3010@_2995</t>
+          <t>_3013@_2995</t>
         </is>
       </c>
     </row>
@@ -962,7 +962,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>29 03</t>
+          <t>29 01 00</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -977,17 +977,17 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Proof Of Ownership</t>
+          <t>Verify Certificate Unidirectional</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Authentication_Proof_Of_Ownership</t>
+          <t>Authentication_Verify_Certificate_Unidirectional</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>($29) Authentication - ProofOfOwnership</t>
+          <t>($29) Authentication - VerifyCertificateUnidirectional</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>_3011@_2995</t>
+          <t>_3009@_2995</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>29 04</t>
+          <t>29 02 00</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -1039,17 +1039,17 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Transmit Certificate</t>
+          <t>Verify Certificate Bidirectional</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Authentication_Transmit_Certificate</t>
+          <t>Authentication_Verify_Certificate_Bidirectional</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>($29) Authentication - Transmit Certificate</t>
+          <t>($29) Authentication - VerifyCertificateBidirectional</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>_3012@_2995</t>
+          <t>_3010@_2995</t>
         </is>
       </c>
     </row>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>29 00</t>
+          <t>29 03</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1101,17 +1101,17 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Deauthentication</t>
+          <t>Proof Of Ownership</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Authentication_Deauthentication</t>
+          <t>Authentication_Proof_Of_Ownership</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>($29) Authentication - DeAuthentication</t>
+          <t>($29) Authentication - ProofOfOwnership</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>_3013@_2995</t>
+          <t>_3011@_2995</t>
         </is>
       </c>
     </row>
@@ -1148,7 +1148,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>29 08</t>
+          <t>29 04</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1163,17 +1163,17 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Authentication Configuration</t>
+          <t>Transmit Certificate</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Authentication_Authentication_Configuration</t>
+          <t>Authentication_Transmit_Certificate</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>($29) Authentication - AuthenticationConfiguration</t>
+          <t>($29) Authentication - Transmit Certificate</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>_3014@_2995</t>
+          <t>_3012@_2995</t>
         </is>
       </c>
     </row>
@@ -1205,57 +1205,57 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>28 00</t>
+          <t>29 08</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Communication Control</t>
+          <t>Authentication</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>EnableRxAndEnableTx</t>
+          <t>Authentication</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>Authentication Configuration</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>EnableRxAndEnableTx_Control</t>
+          <t>Authentication_Authentication_Configuration</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>($28) CommunicationControl</t>
+          <t>($29) Authentication - AuthenticationConfiguration</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>Physical, Functional</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>ExtendedDiagnosticSession</t>
+          <t>All</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>All</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>_3017@_2995</t>
+          <t>_3014@_2995</t>
         </is>
       </c>
     </row>
@@ -1267,42 +1267,42 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>28 01</t>
+          <t>31 01 0531</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Communication Control</t>
+          <t>Routine Control</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>EnableRxAndDisableTx</t>
+          <t>Sensor ID Lock or Unlock Control</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>EnableRxAndDisableTx_Control</t>
+          <t>Sensor_ID_Lock_or_Unlock_Control_Start</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>($28) CommunicationControl</t>
+          <t>($31) RoutineControl - Start routine</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Physical, Functional</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>_3019@_2995</t>
+          <t>_3029@_2995</t>
         </is>
       </c>
     </row>
@@ -1329,42 +1329,42 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>85 01</t>
+          <t>31 01 0601</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Control DTC Setting</t>
+          <t>Routine Control</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Control DTC Setting</t>
+          <t>Sensor Alignment SDC Control</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>On</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>ControlDTCSetting_On</t>
+          <t>Sensor_Alignment_SDC_Control_Start</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>($85) ControlDTCSetting (on)</t>
+          <t>($31) RoutineControl - Start routine</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>Physical, Functional</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1374,12 +1374,12 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>Locked, Unlocked_0x1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>_3021@_2995</t>
+          <t>_3049@_2995</t>
         </is>
       </c>
     </row>
@@ -1391,42 +1391,42 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>85 02</t>
+          <t>31 01 0602</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Control DTC Setting</t>
+          <t>Routine Control</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Control DTC Setting</t>
+          <t>Sensor Alignment EOLC Control</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Off</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>ControlDTCSetting_Off</t>
+          <t>Sensor_Alignment_EOLC_Control_Start</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>($85) ControlDTCSetting (off)</t>
+          <t>($31) RoutineControl - Start routine</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Physical, Functional</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1436,12 +1436,12 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>Locked, Unlocked_0x1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>_3022@_2995</t>
+          <t>_3045@_2995</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>31 01 0531</t>
+          <t>31 01 0603</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Sensor ID Lock or Unlock Control</t>
+          <t>Sensor Alignment AIC Control</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Sensor_ID_Lock_or_Unlock_Control_Start</t>
+          <t>Sensor_Alignment_AIC_Control_Start</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>_3029@_2995</t>
+          <t>_3041@_2995</t>
         </is>
       </c>
     </row>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>31 02 0531</t>
+          <t>31 01 0604</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1530,22 +1530,22 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Sensor ID Lock or Unlock Control</t>
+          <t>Sensor Alignment CDC Control</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Stop</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Sensor_ID_Lock_or_Unlock_Control_Stop</t>
+          <t>Sensor_Alignment_CDC_Control_Start</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>($31) RoutineControl - Stop routine</t>
+          <t>($31) RoutineControl - Start routine</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1565,7 +1565,7 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>_3030@_2995</t>
+          <t>_3037@_2995</t>
         </is>
       </c>
     </row>
@@ -1582,7 +1582,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>31 03 0531</t>
+          <t>31 01 0650</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1592,22 +1592,22 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Sensor ID Lock or Unlock Control</t>
+          <t>Bumper Repair Validation Control</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Request Results</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Sensor_ID_Lock_or_Unlock_Control_RequestResults</t>
+          <t>Bumper_Repair_Validation_Control_Start</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>($31) RoutineControl - Request routine results</t>
+          <t>($31) RoutineControl - Start routine</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -1627,7 +1627,7 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>_3031@_2995</t>
+          <t>_3033@_2995</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>31 01 0650</t>
+          <t>31 02 0531</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1654,22 +1654,22 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Bumper Repair Validation Control</t>
+          <t>Sensor ID Lock or Unlock Control</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Stop</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Bumper_Repair_Validation_Control_Start</t>
+          <t>Sensor_ID_Lock_or_Unlock_Control_Stop</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>($31) RoutineControl - Start routine</t>
+          <t>($31) RoutineControl - Stop routine</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>_3033@_2995</t>
+          <t>_3030@_2995</t>
         </is>
       </c>
     </row>
@@ -1706,7 +1706,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>31 02 0650</t>
+          <t>31 02 0601</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Bumper Repair Validation Control</t>
+          <t>Sensor Alignment SDC Control</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Bumper_Repair_Validation_Control_Stop</t>
+          <t>Sensor_Alignment_SDC_Control_Stop</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1751,7 +1751,7 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>_3034@_2995</t>
+          <t>_3050@_2995</t>
         </is>
       </c>
     </row>
@@ -1768,7 +1768,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>31 03 0650</t>
+          <t>31 02 0602</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1778,22 +1778,22 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Bumper Repair Validation Control</t>
+          <t>Sensor Alignment EOLC Control</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Request Results</t>
+          <t>Stop</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Bumper_Repair_Validation_Control_RequestResults</t>
+          <t>Sensor_Alignment_EOLC_Control_Stop</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>($31) RoutineControl - Request routine results</t>
+          <t>($31) RoutineControl - Stop routine</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>_3035@_2995</t>
+          <t>_3046@_2995</t>
         </is>
       </c>
     </row>
@@ -1830,7 +1830,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>31 01 0604</t>
+          <t>31 02 0603</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1840,22 +1840,22 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Sensor Alignment CDC Control</t>
+          <t>Sensor Alignment AIC Control</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Stop</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Sensor_Alignment_CDC_Control_Start</t>
+          <t>Sensor_Alignment_AIC_Control_Stop</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>($31) RoutineControl - Start routine</t>
+          <t>($31) RoutineControl - Stop routine</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>_3037@_2995</t>
+          <t>_3042@_2995</t>
         </is>
       </c>
     </row>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>31 03 0604</t>
+          <t>31 02 0650</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1964,22 +1964,22 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Sensor Alignment CDC Control</t>
+          <t>Bumper Repair Validation Control</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Request Results</t>
+          <t>Stop</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Sensor_Alignment_CDC_Control_RequestResults</t>
+          <t>Bumper_Repair_Validation_Control_Stop</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>($31) RoutineControl - Request routine results</t>
+          <t>($31) RoutineControl - Stop routine</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>_3039@_2995</t>
+          <t>_3034@_2995</t>
         </is>
       </c>
     </row>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>31 01 0603</t>
+          <t>31 03 0531</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -2026,22 +2026,22 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Sensor Alignment AIC Control</t>
+          <t>Sensor ID Lock or Unlock Control</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Request Results</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Sensor_Alignment_AIC_Control_Start</t>
+          <t>Sensor_ID_Lock_or_Unlock_Control_RequestResults</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>($31) RoutineControl - Start routine</t>
+          <t>($31) RoutineControl - Request routine results</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>_3041@_2995</t>
+          <t>_3031@_2995</t>
         </is>
       </c>
     </row>
@@ -2078,7 +2078,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>31 02 0603</t>
+          <t>31 03 0601</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -2088,22 +2088,22 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Sensor Alignment AIC Control</t>
+          <t>Sensor Alignment SDC Control</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Stop</t>
+          <t>Request Results</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Sensor_Alignment_AIC_Control_Stop</t>
+          <t>Sensor_Alignment_SDC_Control_RequestResults</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>($31) RoutineControl - Stop routine</t>
+          <t>($31) RoutineControl - Request routine results</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>_3042@_2995</t>
+          <t>_3051@_2995</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>31 03 0603</t>
+          <t>31 03 0602</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Sensor Alignment AIC Control</t>
+          <t>Sensor Alignment EOLC Control</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Sensor_Alignment_AIC_Control_RequestResults</t>
+          <t>Sensor_Alignment_EOLC_Control_RequestResults</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2185,7 +2185,7 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>_3043@_2995</t>
+          <t>_3047@_2995</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>31 01 0602</t>
+          <t>31 03 0603</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -2212,22 +2212,22 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Sensor Alignment EOLC Control</t>
+          <t>Sensor Alignment AIC Control</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Request Results</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Sensor_Alignment_EOLC_Control_Start</t>
+          <t>Sensor_Alignment_AIC_Control_RequestResults</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>($31) RoutineControl - Start routine</t>
+          <t>($31) RoutineControl - Request routine results</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>_3045@_2995</t>
+          <t>_3043@_2995</t>
         </is>
       </c>
     </row>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>31 02 0602</t>
+          <t>31 03 0604</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -2274,22 +2274,22 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Sensor Alignment EOLC Control</t>
+          <t>Sensor Alignment CDC Control</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Stop</t>
+          <t>Request Results</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Sensor_Alignment_EOLC_Control_Stop</t>
+          <t>Sensor_Alignment_CDC_Control_RequestResults</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>($31) RoutineControl - Stop routine</t>
+          <t>($31) RoutineControl - Request routine results</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2309,7 +2309,7 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>_3046@_2995</t>
+          <t>_3039@_2995</t>
         </is>
       </c>
     </row>
@@ -2326,7 +2326,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>31 03 0602</t>
+          <t>31 03 0650</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -2336,7 +2336,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Sensor Alignment EOLC Control</t>
+          <t>Bumper Repair Validation Control</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -2346,7 +2346,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Sensor_Alignment_EOLC_Control_RequestResults</t>
+          <t>Bumper_Repair_Validation_Control_RequestResults</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2371,7 +2371,7 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>_3047@_2995</t>
+          <t>_3035@_2995</t>
         </is>
       </c>
     </row>
@@ -2383,57 +2383,57 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>3E</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>31 01 0601</t>
+          <t>3E 00</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Routine Control</t>
+          <t>Tester Present</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Sensor Alignment SDC Control</t>
+          <t>Tester Present</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Send</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Sensor_Alignment_SDC_Control_Start</t>
+          <t>TesterPresent_Send</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>($31) RoutineControl - Start routine</t>
+          <t>($3E) TesterPresent</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Physical, Functional</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>ExtendedDiagnosticSession</t>
+          <t>All</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>All</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>_3049@_2995</t>
+          <t>_3004@_2995</t>
         </is>
       </c>
     </row>
@@ -2445,42 +2445,42 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>85</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>31 02 0601</t>
+          <t>85 01</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Routine Control</t>
+          <t>Control DTC Setting</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Sensor Alignment SDC Control</t>
+          <t>Control DTC Setting</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Stop</t>
+          <t>On</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Sensor_Alignment_SDC_Control_Stop</t>
+          <t>ControlDTCSetting_On</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>($31) RoutineControl - Stop routine</t>
+          <t>($85) ControlDTCSetting (on)</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Physical, Functional</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Locked, Unlocked_0x1</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>_3050@_2995</t>
+          <t>_3021@_2995</t>
         </is>
       </c>
     </row>
@@ -2507,42 +2507,42 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>85</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>31 03 0601</t>
+          <t>85 02</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Routine Control</t>
+          <t>Control DTC Setting</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Sensor Alignment SDC Control</t>
+          <t>Control DTC Setting</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Request Results</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Sensor_Alignment_SDC_Control_RequestResults</t>
+          <t>ControlDTCSetting_Off</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>($31) RoutineControl - Request routine results</t>
+          <t>($85) ControlDTCSetting (off)</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Physical, Functional</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -2552,12 +2552,12 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Locked, Unlocked_0x1</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>_3051@_2995</t>
+          <t>_3022@_2995</t>
         </is>
       </c>
     </row>
@@ -2569,37 +2569,37 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>3E</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>3E 00</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Tester Present</t>
+          <t>Primary Fault Memory</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Tester Present</t>
+          <t>Primary Fault Memory</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Send</t>
+          <t>Clear DTC</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>TesterPresent_Send</t>
+          <t>PrimaryFaultMemory_Clear</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>($3E) TesterPresent</t>
+          <t>($14) ClearDiagnosticInformation</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
@@ -2609,17 +2609,17 @@
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>DefaultSession, ExtendedDiagnosticSession</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Locked, Unlocked_0x1</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>_3004@_3053</t>
+          <t>_3126@_3053</t>
         </is>
       </c>
     </row>
@@ -2631,37 +2631,37 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>27 01</t>
+          <t>19 02</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Security Access</t>
+          <t>Primary Fault Memory</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>request Seed</t>
+          <t>Primary Fault Memory</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Request</t>
+          <t>Read - DTCs by status mask</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>request_Seed_Request</t>
+          <t>PrimaryFaultMemory_ReadAllIdentified</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>($27) SecurityAccess - Request seed</t>
+          <t>($19) ReadDtcInformation - Report DTC by status mask</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2671,17 +2671,17 @@
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>ProgrammingSession, ExtendedDiagnosticSession</t>
+          <t>DefaultSession, ExtendedDiagnosticSession</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Locked, Unlocked_0x1</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>_3058@_3053</t>
+          <t>_3122@_3053</t>
         </is>
       </c>
     </row>
@@ -2693,37 +2693,37 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>27 02</t>
+          <t>19 04</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Security Access</t>
+          <t>Primary Fault Memory</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>sendKey</t>
+          <t>Primary Fault Memory</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Send</t>
+          <t>Read - snapshot record</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>sendKey_Send</t>
+          <t>PrimaryFaultMemory_Read_snapshot_record</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>($27) SecurityAccess - Send key</t>
+          <t>($19) ReadDtcInformation - Report DTC Snapshot Record by DTC Number</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
@@ -2733,17 +2733,17 @@
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>ProgrammingSession, ExtendedDiagnosticSession</t>
+          <t>DefaultSession, ExtendedDiagnosticSession</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Locked, Unlocked_0x1</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>_3060@_3053</t>
+          <t>_3124@_3053</t>
         </is>
       </c>
     </row>
@@ -2755,57 +2755,57 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>28 03</t>
+          <t>19 06</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Communication Control</t>
+          <t>Primary Fault Memory</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>DisableRxAndTx</t>
+          <t>Primary Fault Memory</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>Read - extended data record</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>DisableRxAndTx_Control</t>
+          <t>PrimaryFaultMemory_Read_extended_data_record</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>($28) CommunicationControl</t>
+          <t>($19) ReadDtcInformation - Report DTC Extended Data Record by DTC Number</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>Physical, Functional</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>ExtendedDiagnosticSession</t>
+          <t>DefaultSession, ExtendedDiagnosticSession</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Locked, Unlocked_0x1</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>_3063@_3053</t>
+          <t>_3123@_3053</t>
         </is>
       </c>
     </row>
@@ -2817,47 +2817,47 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>85 01</t>
+          <t>19 0A</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Control DTC Setting</t>
+          <t>Primary Fault Memory</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Control DTC Setting</t>
+          <t>Primary Fault Memory</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>On</t>
+          <t>Read - supported DTCs</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>ControlDTCSetting_On</t>
+          <t>PrimaryFaultMemory_ReadAllSupported</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>($85) ControlDTCSetting (on)</t>
+          <t>($19) ReadDtcInformation - Report supported DTC</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>Physical, Functional</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>ExtendedDiagnosticSession</t>
+          <t>DefaultSession, ExtendedDiagnosticSession</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>_3021@_3053</t>
+          <t>_3125@_3053</t>
         </is>
       </c>
     </row>
@@ -2879,37 +2879,37 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>85 02</t>
+          <t>22 0460</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Control DTC Setting</t>
+          <t>Identification</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Control DTC Setting</t>
+          <t>PCANDevelopmentDataControl</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Off</t>
+          <t>Read</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>ControlDTCSetting_Off</t>
+          <t>PCANDevelopmentDataControl_Read</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>($85) ControlDTCSetting (off)</t>
+          <t>($22) ReadDataByIdentifier</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>ExtendedDiagnosticSession</t>
+          <t>DefaultSession, ExtendedDiagnosticSession</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>Locked, Unlocked_0x1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>_3022@_3053</t>
+          <t>_3084@_3053</t>
         </is>
       </c>
     </row>
@@ -2946,17 +2946,17 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>22 F18C</t>
+          <t>22 4900</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Identification</t>
+          <t>Measurements</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>ECU Serial Number</t>
+          <t>CR parameter configuration</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>ECU_Serial_Number_Read</t>
+          <t>CR_parameter_configuration_Read</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Physical, Functional</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>Locked, Unlocked_0x1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>_3065@_3053</t>
+          <t>_3097@_3053</t>
         </is>
       </c>
     </row>
@@ -3008,17 +3008,17 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>22 F089</t>
+          <t>22 4901</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Identification</t>
+          <t>IO Control</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Vehicle Manufacturer ECU Hardware Version Number Data Identifier</t>
+          <t>BSD modulel IO Status</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Vehicle_Manufacturer_ECU_Hardware_Version_Number_Data_Identifier_Read</t>
+          <t>BSD_modulel_IO_Status_Read</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -3038,22 +3038,22 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Physical, Functional</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>DefaultSession, ExtendedDiagnosticSession</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>_3066@_3053</t>
+          <t>_3105@_3053</t>
         </is>
       </c>
     </row>
@@ -3070,17 +3070,17 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>22 F160</t>
+          <t>22 4902</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Identification</t>
+          <t>Measurements</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Signature Public Key Status</t>
+          <t>Get Calibration Angle</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -3090,7 +3090,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Signature_Public_Key_Status_Read</t>
+          <t>Get_Calibration_Angle_Read</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3100,7 +3100,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Physical, Functional</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -3115,7 +3115,7 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>_3067@_3053</t>
+          <t>_3095@_3053</t>
         </is>
       </c>
     </row>
@@ -3132,17 +3132,17 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>22 F195</t>
+          <t>22 4903</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Identification</t>
+          <t>Measurements</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>System Supplier ECU Software Version Number</t>
+          <t>Request System State</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>System_Supplier_ECU_Software_Version_Number_Read</t>
+          <t>Request_System_State_Read</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Physical, Functional</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -3177,7 +3177,7 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>_3068@_3053</t>
+          <t>_3098@_3053</t>
         </is>
       </c>
     </row>
@@ -3194,17 +3194,17 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>22 F197</t>
+          <t>22 4905</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Identification</t>
+          <t>IO Control</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>System Name</t>
+          <t>Request  Angle Calibration</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -3214,7 +3214,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>System_Name_Read</t>
+          <t>Request_Angle_Calibration_Read</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Physical, Functional</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -3239,7 +3239,7 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>_3069@_3053</t>
+          <t>_3108@_3053</t>
         </is>
       </c>
     </row>
@@ -3256,17 +3256,17 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>22 F193</t>
+          <t>22 4907</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Identification</t>
+          <t>Measurements</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>System Supplier ECU Hardware Version Number Data Identifier</t>
+          <t>Get Angle Calibration state</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -3276,7 +3276,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>System_Supplier_ECU_Hardware_Version_Number_Data_Identifier_Read</t>
+          <t>Get_Angle_Calibration_state_Read</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Physical, Functional</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -3301,7 +3301,7 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>_3070@_3053</t>
+          <t>_3096@_3053</t>
         </is>
       </c>
     </row>
@@ -3318,17 +3318,17 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>22 F18A</t>
+          <t>22 4908</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Identification</t>
+          <t>Measurements</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>System Supplier Identifier Data Identifier</t>
+          <t>Get snapshot</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -3338,7 +3338,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>System_Supplier_Identifier_Data_Identifier_Read</t>
+          <t>Get_snapshot_Read</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3348,7 +3348,7 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Physical, Functional</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -3363,7 +3363,7 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>_3071@_3053</t>
+          <t>_3094@_3053</t>
         </is>
       </c>
     </row>
@@ -3380,17 +3380,17 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>22 F187</t>
+          <t>22 E680</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Identification</t>
+          <t>Measurements</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Vehicle Manufacturer Spare Part Number Data Identifier</t>
+          <t>Current Time</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -3400,7 +3400,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Vehicle_Manufacturer_Spare_Part_Number_Data_Identifier_Read</t>
+          <t>Current_Time_Read</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -3410,22 +3410,22 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Physical, Functional</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>DefaultSession, ExtendedDiagnosticSession</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Locked, Unlocked_0x1</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>_3072@_3053</t>
+          <t>_3099@_3053</t>
         </is>
       </c>
     </row>
@@ -3442,17 +3442,17 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>22 F184</t>
+          <t>22 E681</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Identification</t>
+          <t>Measurements</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Application Software Fingerprint Data Identifier</t>
+          <t>Vehicle Speed</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -3462,7 +3462,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Application_Software_Fingerprint_Data_Identifier_Read</t>
+          <t>Vehicle_Speed_Read</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -3472,22 +3472,22 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Physical, Functional</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>DefaultSession, ExtendedDiagnosticSession</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Locked, Unlocked_0x1</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>_3073@_3053</t>
+          <t>_3100@_3053</t>
         </is>
       </c>
     </row>
@@ -3499,57 +3499,57 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>2E</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>2E F184</t>
+          <t>22 E682</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Identification</t>
+          <t>Measurements</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Application Software Fingerprint Data Identifier</t>
+          <t>Total Odometer</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>Write</t>
+          <t>Read</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Application_Software_Fingerprint_Data_Identifier_Write</t>
+          <t>Total_Odometer_Read</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>($2E) WriteDataByIdentifier</t>
+          <t>($22) ReadDataByIdentifier</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Physical, Functional</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>ProgrammingSession</t>
+          <t>DefaultSession, ExtendedDiagnosticSession</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>Unlocked_0x11</t>
+          <t>Locked, Unlocked_0x1</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>_3074@_3053</t>
+          <t>_3101@_3053</t>
         </is>
       </c>
     </row>
@@ -3566,17 +3566,17 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>22 F190</t>
+          <t>22 E683</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Identification</t>
+          <t>Measurements</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>VIN Data Identifier</t>
+          <t>Current Voltage</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -3586,7 +3586,7 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>VIN_Data_Identifier_Read</t>
+          <t>Current_Voltage_Read</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -3596,7 +3596,7 @@
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Physical, Functional</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>_3075@_3053</t>
+          <t>_3102@_3053</t>
         </is>
       </c>
     </row>
@@ -3623,12 +3623,12 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>2E</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>2E F190</t>
+          <t>22 F013</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -3638,22 +3638,22 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>VIN Data Identifier</t>
+          <t>Vehicle Manufacturer Logistic Software Part Number</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>Write</t>
+          <t>Read</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>VIN_Data_Identifier_Write</t>
+          <t>Vehicle_Manufacturer_Logistic_Software_Part_Number_Read</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>($2E) WriteDataByIdentifier</t>
+          <t>($22) ReadDataByIdentifier</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
@@ -3663,17 +3663,17 @@
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>ExtendedDiagnosticSession</t>
+          <t>All</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>Unlocked_0x1</t>
+          <t>All</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>_3076@_3053</t>
+          <t>_3079@_3053</t>
         </is>
       </c>
     </row>
@@ -3690,7 +3690,7 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>22 F189</t>
+          <t>22 F031</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -3700,7 +3700,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Vehicle Manufacturer ECU Software Version Number Data Identifier</t>
+          <t>Vehicle Manufacturer Calibration Data Part Number</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Vehicle_Manufacturer_ECU_Software_Version_Number_Data_Identifier_Read</t>
+          <t>Vehicle_Manufacturer_Calibration_Data_Part_Number_Read</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -3720,7 +3720,7 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Physical, Functional</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -3735,7 +3735,7 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>_3077@_3053</t>
+          <t>_3083@_3053</t>
         </is>
       </c>
     </row>
@@ -3752,7 +3752,7 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>22 F180</t>
+          <t>22 F089</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -3762,7 +3762,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Boot Software Identification</t>
+          <t>Vehicle Manufacturer ECU Hardware Version Number Data Identifier</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -3772,7 +3772,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Boot_Software_Identification_Read</t>
+          <t>Vehicle_Manufacturer_ECU_Hardware_Version_Number_Data_Identifier_Read</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>_3078@_3053</t>
+          <t>_3066@_3053</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>22 F013</t>
+          <t>22 F090</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -3824,7 +3824,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Vehicle Manufacturer Logistic Software Part Number</t>
+          <t>Vehicle Manufacturer ECU Backup Software Version Number Data Identifier</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -3834,7 +3834,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Vehicle_Manufacturer_Logistic_Software_Part_Number_Read</t>
+          <t>Vehicle_Manufacturer_ECU_Backup_Software_Version_Number_Data_Identifier_Read</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -3844,22 +3844,22 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Physical, Functional</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>DefaultSession, ExtendedDiagnosticSession</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Locked, Unlocked_0x1</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>_3079@_3053</t>
+          <t>_3087@_3053</t>
         </is>
       </c>
     </row>
@@ -3876,7 +3876,7 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>22 F0F1</t>
+          <t>22 F091</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -3886,7 +3886,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Update Tried Counter</t>
+          <t>Mapping between DTC and DTC Number</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -3896,7 +3896,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Update_Tried_Counter_Read</t>
+          <t>Mapping_between_DTC_and_DTC_Number_Read</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -3906,22 +3906,22 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Physical, Functional</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>DefaultSession, ExtendedDiagnosticSession</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Locked, Unlocked_0x1</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>_3080@_3053</t>
+          <t>_3089@_3053</t>
         </is>
       </c>
     </row>
@@ -3938,7 +3938,7 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>22 F0F3</t>
+          <t>22 F0F0</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -3948,7 +3948,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Dependecy Check Success Counter</t>
+          <t>RunningAreaInfo</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -3958,7 +3958,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Dependecy_Check_Success_Counter_Read</t>
+          <t>RunningAreaInfo_Read</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -3968,7 +3968,7 @@
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Physical, Functional</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -3983,7 +3983,7 @@
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>_3081@_3053</t>
+          <t>_3086@_3053</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>22 F186</t>
+          <t>22 F0F1</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -4010,7 +4010,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Active Diagnostic Session</t>
+          <t>Update Tried Counter</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -4020,7 +4020,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Active_Diagnostic_Session_Read</t>
+          <t>Update_Tried_Counter_Read</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -4045,7 +4045,7 @@
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>_3082@_3053</t>
+          <t>_3080@_3053</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>22 F031</t>
+          <t>22 F0F3</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Vehicle Manufacturer Calibration Data Part Number</t>
+          <t>Dependecy Check Success Counter</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -4082,7 +4082,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>Vehicle_Manufacturer_Calibration_Data_Part_Number_Read</t>
+          <t>Dependecy_Check_Success_Counter_Read</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -4092,22 +4092,22 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>Physical, Functional</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>DefaultSession, ExtendedDiagnosticSession</t>
+          <t>All</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>Locked, Unlocked_0x1</t>
+          <t>All</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>_3083@_3053</t>
+          <t>_3081@_3053</t>
         </is>
       </c>
     </row>
@@ -4124,7 +4124,7 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>22 0460</t>
+          <t>22 F107</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -4134,7 +4134,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>PCANDevelopmentDataControl</t>
+          <t>Vehicle Manufacture ECU Application Diagnostic Database Part And Version Number</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>PCANDevelopmentDataControl_Read</t>
+          <t>Vehicle_Manufacture_ECU_Application_Diagnostic_Database_Part_And_Version_Number_Read</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -4164,12 +4164,12 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Locked, Unlocked_0x1</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>_3084@_3053</t>
+          <t>_3092@_3053</t>
         </is>
       </c>
     </row>
@@ -4181,12 +4181,12 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>2E</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>2E 0460</t>
+          <t>22 F160</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -4196,22 +4196,22 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>PCANDevelopmentDataControl</t>
+          <t>Signature Public Key Status</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>Write</t>
+          <t>Read</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>PCANDevelopmentDataControl_Write</t>
+          <t>Signature_Public_Key_Status_Read</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>($2E) WriteDataByIdentifier</t>
+          <t>($22) ReadDataByIdentifier</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
@@ -4221,17 +4221,17 @@
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>ExtendedDiagnosticSession</t>
+          <t>DefaultSession, ExtendedDiagnosticSession</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>Unlocked_0x1</t>
+          <t>Locked, Unlocked_0x1</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>_3085@_3053</t>
+          <t>_3067@_3053</t>
         </is>
       </c>
     </row>
@@ -4248,7 +4248,7 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>22 F0F0</t>
+          <t>22 F162</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -4258,7 +4258,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>RunningAreaInfo</t>
+          <t>Hash value of the current application software version</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -4268,7 +4268,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>RunningAreaInfo_Read</t>
+          <t>Hash_value_of_the_current_application_software_version_Read</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -4283,17 +4283,17 @@
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>DefaultSession, ExtendedDiagnosticSession</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Locked, Unlocked_0x1</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>_3086@_3053</t>
+          <t>_3090@_3053</t>
         </is>
       </c>
     </row>
@@ -4310,7 +4310,7 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>22 F090</t>
+          <t>22 F163</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -4320,7 +4320,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Vehicle Manufacturer ECU Backup Software Version Number Data Identifier</t>
+          <t>Hash value of the current calibration software version</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -4330,7 +4330,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Vehicle_Manufacturer_ECU_Backup_Software_Version_Number_Data_Identifier_Read</t>
+          <t>Hash_value_of_the_current_calibration_software_version_Read</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -4355,7 +4355,7 @@
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>_3087@_3053</t>
+          <t>_3091@_3053</t>
         </is>
       </c>
     </row>
@@ -4372,7 +4372,7 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>22 F18B</t>
+          <t>22 F180</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -4382,7 +4382,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>ECU manufacturing date</t>
+          <t>Boot Software Identification</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>ECU_manufacturing_date_Read</t>
+          <t>Boot_Software_Identification_Read</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -4402,22 +4402,22 @@
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>Physical, Functional</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>DefaultSession, ExtendedDiagnosticSession</t>
+          <t>All</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>Locked, Unlocked_0x1</t>
+          <t>All</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>_3088@_3053</t>
+          <t>_3078@_3053</t>
         </is>
       </c>
     </row>
@@ -4434,7 +4434,7 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>22 F091</t>
+          <t>22 F184</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -4444,7 +4444,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Mapping between DTC and DTC Number</t>
+          <t>Application Software Fingerprint Data Identifier</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -4454,7 +4454,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Mapping_between_DTC_and_DTC_Number_Read</t>
+          <t>Application_Software_Fingerprint_Data_Identifier_Read</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -4464,22 +4464,22 @@
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>Physical, Functional</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>DefaultSession, ExtendedDiagnosticSession</t>
+          <t>All</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>Locked, Unlocked_0x1</t>
+          <t>All</t>
         </is>
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>_3089@_3053</t>
+          <t>_3073@_3053</t>
         </is>
       </c>
     </row>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>22 F162</t>
+          <t>22 F186</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -4506,7 +4506,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Hash value of the current application software version</t>
+          <t>Active Diagnostic Session</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -4516,7 +4516,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Hash_value_of_the_current_application_software_version_Read</t>
+          <t>Active_Diagnostic_Session_Read</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -4526,22 +4526,22 @@
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>Physical, Functional</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>DefaultSession, ExtendedDiagnosticSession</t>
+          <t>All</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>Locked, Unlocked_0x1</t>
+          <t>All</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>_3090@_3053</t>
+          <t>_3082@_3053</t>
         </is>
       </c>
     </row>
@@ -4558,7 +4558,7 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>22 F163</t>
+          <t>22 F187</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -4568,7 +4568,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Hash value of the current calibration software version</t>
+          <t>Vehicle Manufacturer Spare Part Number Data Identifier</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -4578,7 +4578,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>Hash_value_of_the_current_calibration_software_version_Read</t>
+          <t>Vehicle_Manufacturer_Spare_Part_Number_Data_Identifier_Read</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -4588,22 +4588,22 @@
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>Physical, Functional</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>DefaultSession, ExtendedDiagnosticSession</t>
+          <t>All</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>Locked, Unlocked_0x1</t>
+          <t>All</t>
         </is>
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>_3091@_3053</t>
+          <t>_3072@_3053</t>
         </is>
       </c>
     </row>
@@ -4620,7 +4620,7 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>22 F107</t>
+          <t>22 F189</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -4630,7 +4630,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Vehicle Manufacture ECU Application Diagnostic Database Part And Version Number</t>
+          <t>Vehicle Manufacturer ECU Software Version Number Data Identifier</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -4640,7 +4640,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Vehicle_Manufacture_ECU_Application_Diagnostic_Database_Part_And_Version_Number_Read</t>
+          <t>Vehicle_Manufacturer_ECU_Software_Version_Number_Data_Identifier_Read</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -4650,7 +4650,7 @@
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>Physical, Functional</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
@@ -4665,7 +4665,7 @@
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>_3092@_3053</t>
+          <t>_3077@_3053</t>
         </is>
       </c>
     </row>
@@ -4682,17 +4682,17 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>22 4908</t>
+          <t>22 F18A</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Measurements</t>
+          <t>Identification</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>Get snapshot</t>
+          <t>System Supplier Identifier Data Identifier</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -4702,7 +4702,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>Get_snapshot_Read</t>
+          <t>System_Supplier_Identifier_Data_Identifier_Read</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>Physical, Functional</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
@@ -4727,7 +4727,7 @@
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>_3094@_3053</t>
+          <t>_3071@_3053</t>
         </is>
       </c>
     </row>
@@ -4744,17 +4744,17 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>22 4902</t>
+          <t>22 F18B</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Measurements</t>
+          <t>Identification</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Get Calibration Angle</t>
+          <t>ECU manufacturing date</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -4764,7 +4764,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Get_Calibration_Angle_Read</t>
+          <t>ECU_manufacturing_date_Read</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -4789,7 +4789,7 @@
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>_3095@_3053</t>
+          <t>_3088@_3053</t>
         </is>
       </c>
     </row>
@@ -4806,17 +4806,17 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>22 4907</t>
+          <t>22 F18C</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Measurements</t>
+          <t>Identification</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Get Angle Calibration state</t>
+          <t>ECU Serial Number</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>Get_Angle_Calibration_state_Read</t>
+          <t>ECU_Serial_Number_Read</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -4836,22 +4836,22 @@
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>Physical, Functional</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>DefaultSession, ExtendedDiagnosticSession</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Locked, Unlocked_0x1</t>
         </is>
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>_3096@_3053</t>
+          <t>_3065@_3053</t>
         </is>
       </c>
     </row>
@@ -4868,17 +4868,17 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>22 4900</t>
+          <t>22 F190</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Measurements</t>
+          <t>Identification</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>CR parameter configuration</t>
+          <t>VIN Data Identifier</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>CR_parameter_configuration_Read</t>
+          <t>VIN_Data_Identifier_Read</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -4898,7 +4898,7 @@
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>Physical, Functional</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
@@ -4908,12 +4908,12 @@
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Locked, Unlocked_0x1</t>
         </is>
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>_3097@_3053</t>
+          <t>_3075@_3053</t>
         </is>
       </c>
     </row>
@@ -4930,17 +4930,17 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>22 4903</t>
+          <t>22 F193</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Measurements</t>
+          <t>Identification</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>Request System State</t>
+          <t>System Supplier ECU Hardware Version Number Data Identifier</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -4950,7 +4950,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>Request_System_State_Read</t>
+          <t>System_Supplier_ECU_Hardware_Version_Number_Data_Identifier_Read</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -4960,22 +4960,22 @@
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>Physical, Functional</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>DefaultSession, ExtendedDiagnosticSession</t>
+          <t>All</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>Locked, Unlocked_0x1</t>
+          <t>All</t>
         </is>
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>_3098@_3053</t>
+          <t>_3070@_3053</t>
         </is>
       </c>
     </row>
@@ -4992,17 +4992,17 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>22 E680</t>
+          <t>22 F195</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Measurements</t>
+          <t>Identification</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Current Time</t>
+          <t>System Supplier ECU Software Version Number</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -5012,7 +5012,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Current_Time_Read</t>
+          <t>System_Supplier_ECU_Software_Version_Number_Read</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -5022,7 +5022,7 @@
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>Physical, Functional</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -5037,7 +5037,7 @@
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>_3099@_3053</t>
+          <t>_3068@_3053</t>
         </is>
       </c>
     </row>
@@ -5054,17 +5054,17 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>22 E681</t>
+          <t>22 F197</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Measurements</t>
+          <t>Identification</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Vehicle Speed</t>
+          <t>System Name</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -5074,7 +5074,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Vehicle_Speed_Read</t>
+          <t>System_Name_Read</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -5084,7 +5084,7 @@
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>Physical, Functional</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>_3100@_3053</t>
+          <t>_3069@_3053</t>
         </is>
       </c>
     </row>
@@ -5111,57 +5111,57 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>22 E682</t>
+          <t>27 01</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Measurements</t>
+          <t>Security Access</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Total Odometer</t>
+          <t>request Seed</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>Read</t>
+          <t>Request</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Total_Odometer_Read</t>
+          <t>request_Seed_Request</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>($22) ReadDataByIdentifier</t>
+          <t>($27) SecurityAccess - Request seed</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>Physical, Functional</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>DefaultSession, ExtendedDiagnosticSession</t>
+          <t>ProgrammingSession, ExtendedDiagnosticSession</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>Locked, Unlocked_0x1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>_3101@_3053</t>
+          <t>_3058@_3053</t>
         </is>
       </c>
     </row>
@@ -5173,57 +5173,57 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>22 E683</t>
+          <t>27 02</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Measurements</t>
+          <t>Security Access</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Current Voltage</t>
+          <t>sendKey</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>Read</t>
+          <t>Send</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>Current_Voltage_Read</t>
+          <t>sendKey_Send</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>($22) ReadDataByIdentifier</t>
+          <t>($27) SecurityAccess - Send key</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>Physical, Functional</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>DefaultSession, ExtendedDiagnosticSession</t>
+          <t>ProgrammingSession, ExtendedDiagnosticSession</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>Locked, Unlocked_0x1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>_3102@_3053</t>
+          <t>_3060@_3053</t>
         </is>
       </c>
     </row>
@@ -5235,37 +5235,37 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>22 4901</t>
+          <t>28 03</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>IO Control</t>
+          <t>Communication Control</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>BSD modulel IO Status</t>
+          <t>DisableRxAndTx</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>Read</t>
+          <t>Control</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>BSD_modulel_IO_Status_Read</t>
+          <t>DisableRxAndTx_Control</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>($22) ReadDataByIdentifier</t>
+          <t>($28) CommunicationControl</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
@@ -5275,7 +5275,7 @@
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>DefaultSession, ExtendedDiagnosticSession</t>
+          <t>ExtendedDiagnosticSession</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -5285,7 +5285,7 @@
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>_3105@_3053</t>
+          <t>_3063@_3053</t>
         </is>
       </c>
     </row>
@@ -5297,37 +5297,37 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>2F</t>
+          <t>2E</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>2F 4901 00</t>
+          <t>2E 0460</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>IO Control</t>
+          <t>Identification</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>BSD modulel IO Status</t>
+          <t>PCANDevelopmentDataControl</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>ReturnControl</t>
+          <t>Write</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>BSD_modulel_IO_Status_ReturnControl</t>
+          <t>PCANDevelopmentDataControl_Write</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>($2F) InputOutputControlByIdentifier - Return control to ECU</t>
+          <t>($2E) WriteDataByIdentifier</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
@@ -5342,12 +5342,12 @@
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Unlocked_0x1</t>
         </is>
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>_3106@_3053</t>
+          <t>_3085@_3053</t>
         </is>
       </c>
     </row>
@@ -5359,37 +5359,37 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>2F</t>
+          <t>2E</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>2F 4901 03</t>
+          <t>2E F184</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>IO Control</t>
+          <t>Identification</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>BSD modulel IO Status</t>
+          <t>Application Software Fingerprint Data Identifier</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>Write</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>BSD_modulel_IO_Status_Control</t>
+          <t>Application_Software_Fingerprint_Data_Identifier_Write</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>($2F) InputOutputControlByIdentifier - Short term adjustment</t>
+          <t>($2E) WriteDataByIdentifier</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
@@ -5399,17 +5399,17 @@
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>ExtendedDiagnosticSession</t>
+          <t>ProgrammingSession</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Unlocked_0x11</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>_3107@_3053</t>
+          <t>_3074@_3053</t>
         </is>
       </c>
     </row>
@@ -5421,57 +5421,57 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2E</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>22 4905</t>
+          <t>2E F190</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>IO Control</t>
+          <t>Identification</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>Request  Angle Calibration</t>
+          <t>VIN Data Identifier</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>Read</t>
+          <t>Write</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>Request_Angle_Calibration_Read</t>
+          <t>VIN_Data_Identifier_Write</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>($22) ReadDataByIdentifier</t>
+          <t>($2E) WriteDataByIdentifier</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>Physical, Functional</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>DefaultSession, ExtendedDiagnosticSession</t>
+          <t>ExtendedDiagnosticSession</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>Locked, Unlocked_0x1</t>
+          <t>Unlocked_0x1</t>
         </is>
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>_3108@_3053</t>
+          <t>_3076@_3053</t>
         </is>
       </c>
     </row>
@@ -5488,7 +5488,7 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>2F 4905 00</t>
+          <t>2F 4901 00</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -5498,7 +5498,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Request  Angle Calibration</t>
+          <t>BSD modulel IO Status</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -5508,7 +5508,7 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>Request_Angle_Calibration_ReturnControl</t>
+          <t>BSD_modulel_IO_Status_ReturnControl</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -5528,12 +5528,12 @@
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>Unlocked_0x1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>_3109@_3053</t>
+          <t>_3106@_3053</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>2F 4905 03</t>
+          <t>2F 4901 03</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
@@ -5560,7 +5560,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>Request  Angle Calibration</t>
+          <t>BSD modulel IO Status</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -5570,7 +5570,7 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>Request_Angle_Calibration_Control</t>
+          <t>BSD_modulel_IO_Status_Control</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>Unlocked_0x1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>_3110@_3053</t>
+          <t>_3107@_3053</t>
         </is>
       </c>
     </row>
@@ -5607,37 +5607,37 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>2F</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>31 01 0203</t>
+          <t>2F 4905 00</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Routine Control</t>
+          <t>IO Control</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Programming Precondition Check</t>
+          <t>Request  Angle Calibration</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>ReturnControl</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>Programming_Precondition_Check_Start</t>
+          <t>Request_Angle_Calibration_ReturnControl</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>($31) RoutineControl - Start routine</t>
+          <t>($2F) InputOutputControlByIdentifier - Return control to ECU</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
@@ -5652,12 +5652,12 @@
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>Locked</t>
+          <t>Unlocked_0x1</t>
         </is>
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>_3113@_3053</t>
+          <t>_3109@_3053</t>
         </is>
       </c>
     </row>
@@ -5669,37 +5669,37 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>2F</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>31 01 0531</t>
+          <t>2F 4905 03</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Routine Control</t>
+          <t>IO Control</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>Lock and Unlock Sensor Identification</t>
+          <t>Request  Angle Calibration</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Control</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>Lock_and_Unlock_Sensor_Identification_Start</t>
+          <t>Request_Angle_Calibration_Control</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>($31) RoutineControl - Start routine</t>
+          <t>($2F) InputOutputControlByIdentifier - Short term adjustment</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>_3115@_3053</t>
+          <t>_3110@_3053</t>
         </is>
       </c>
     </row>
@@ -5736,7 +5736,7 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>31 02 0531</t>
+          <t>31 01 0203</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -5746,22 +5746,22 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Lock and Unlock Sensor Identification</t>
+          <t>Programming Precondition Check</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>Stop</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>Lock_and_Unlock_Sensor_Identification_Stop</t>
+          <t>Programming_Precondition_Check_Start</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>($31) RoutineControl - Stop routine</t>
+          <t>($31) RoutineControl - Start routine</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
@@ -5776,12 +5776,12 @@
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>Unlocked_0x1</t>
+          <t>Locked</t>
         </is>
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>_3116@_3053</t>
+          <t>_3113@_3053</t>
         </is>
       </c>
     </row>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>31 03 0531</t>
+          <t>31 01 0531</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
@@ -5813,17 +5813,17 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>Request Results</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>Lock_and_Unlock_Sensor_Identification_RequestResults</t>
+          <t>Lock_and_Unlock_Sensor_Identification_Start</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>($31) RoutineControl - Request routine results</t>
+          <t>($31) RoutineControl - Start routine</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
@@ -5843,7 +5843,7 @@
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>_3117@_3053</t>
+          <t>_3115@_3053</t>
         </is>
       </c>
     </row>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>31 03 DD04</t>
+          <t>31 02 0531</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
@@ -5932,22 +5932,22 @@
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>Version switchover</t>
+          <t>Lock and Unlock Sensor Identification</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>Request Results</t>
+          <t>Stop</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>Version_switchover_RequestResults</t>
+          <t>Lock_and_Unlock_Sensor_Identification_Stop</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>($31) RoutineControl - Request routine results</t>
+          <t>($31) RoutineControl - Stop routine</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
@@ -5957,17 +5957,17 @@
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>ProgrammingSession, ExtendedDiagnosticSession</t>
+          <t>ExtendedDiagnosticSession</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Unlocked_0x1</t>
         </is>
       </c>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>_3120@_3053</t>
+          <t>_3116@_3053</t>
         </is>
       </c>
     </row>
@@ -5979,37 +5979,37 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>19 02</t>
+          <t>31 03 0531</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Primary Fault Memory</t>
+          <t>Routine Control</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>Primary Fault Memory</t>
+          <t>Lock and Unlock Sensor Identification</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>Read - DTCs by status mask</t>
+          <t>Request Results</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>PrimaryFaultMemory_ReadAllIdentified</t>
+          <t>Lock_and_Unlock_Sensor_Identification_RequestResults</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>($19) ReadDtcInformation - Report DTC by status mask</t>
+          <t>($31) RoutineControl - Request routine results</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
@@ -6019,17 +6019,17 @@
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>DefaultSession, ExtendedDiagnosticSession</t>
+          <t>ExtendedDiagnosticSession</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>Locked, Unlocked_0x1</t>
+          <t>Unlocked_0x1</t>
         </is>
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>_3122@_3053</t>
+          <t>_3117@_3053</t>
         </is>
       </c>
     </row>
@@ -6041,37 +6041,37 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>19 06</t>
+          <t>31 03 DD04</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Primary Fault Memory</t>
+          <t>Routine Control</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>Primary Fault Memory</t>
+          <t>Version switchover</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>Read - extended data record</t>
+          <t>Request Results</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>PrimaryFaultMemory_Read_extended_data_record</t>
+          <t>Version_switchover_RequestResults</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>($19) ReadDtcInformation - Report DTC Extended Data Record by DTC Number</t>
+          <t>($31) RoutineControl - Request routine results</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
@@ -6081,17 +6081,17 @@
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>DefaultSession, ExtendedDiagnosticSession</t>
+          <t>ProgrammingSession, ExtendedDiagnosticSession</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>Locked, Unlocked_0x1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>_3123@_3053</t>
+          <t>_3120@_3053</t>
         </is>
       </c>
     </row>
@@ -6103,57 +6103,57 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>3E</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>19 04</t>
+          <t>3E 00</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Primary Fault Memory</t>
+          <t>Tester Present</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>Primary Fault Memory</t>
+          <t>Tester Present</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>Read - snapshot record</t>
+          <t>Send</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>PrimaryFaultMemory_Read_snapshot_record</t>
+          <t>TesterPresent_Send</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>($19) ReadDtcInformation - Report DTC Snapshot Record by DTC Number</t>
+          <t>($3E) TesterPresent</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Physical, Functional</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>DefaultSession, ExtendedDiagnosticSession</t>
+          <t>All</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>Locked, Unlocked_0x1</t>
+          <t>All</t>
         </is>
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>_3124@_3053</t>
+          <t>_3004@_3053</t>
         </is>
       </c>
     </row>
@@ -6165,47 +6165,47 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>85</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>19 0A</t>
+          <t>85 01</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>Primary Fault Memory</t>
+          <t>Control DTC Setting</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>Primary Fault Memory</t>
+          <t>Control DTC Setting</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>Read - supported DTCs</t>
+          <t>On</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>PrimaryFaultMemory_ReadAllSupported</t>
+          <t>ControlDTCSetting_On</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>($19) ReadDtcInformation - Report supported DTC</t>
+          <t>($85) ControlDTCSetting (on)</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Physical, Functional</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>DefaultSession, ExtendedDiagnosticSession</t>
+          <t>ExtendedDiagnosticSession</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
@@ -6215,7 +6215,7 @@
       </c>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>_3125@_3053</t>
+          <t>_3021@_3053</t>
         </is>
       </c>
     </row>
@@ -6227,37 +6227,37 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>85</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>85 02</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Primary Fault Memory</t>
+          <t>Control DTC Setting</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>Primary Fault Memory</t>
+          <t>Control DTC Setting</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>Clear DTC</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>PrimaryFaultMemory_Clear</t>
+          <t>ControlDTCSetting_Off</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>($14) ClearDiagnosticInformation</t>
+          <t>($85) ControlDTCSetting (off)</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
@@ -6267,7 +6267,7 @@
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>DefaultSession, ExtendedDiagnosticSession</t>
+          <t>ExtendedDiagnosticSession</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
@@ -6277,7 +6277,7 @@
       </c>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>_3126@_3053</t>
+          <t>_3022@_3053</t>
         </is>
       </c>
     </row>
@@ -6289,37 +6289,37 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>3E</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>3E 00</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Tester Present</t>
+          <t>Primary Fault Memory</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>Tester Present</t>
+          <t>Primary Fault Memory</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>Send</t>
+          <t>Clear DTC</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>TesterPresent_Send</t>
+          <t>PrimaryFaultMemory_Clear</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>($3E) TesterPresent</t>
+          <t>($14) ClearDiagnosticInformation</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
@@ -6329,17 +6329,17 @@
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>DefaultSession, ExtendedDiagnosticSession</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>_3004@_3159</t>
+          <t>_3220@_3159</t>
         </is>
       </c>
     </row>
@@ -6351,37 +6351,37 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>27 11</t>
+          <t>19 01</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Security Access</t>
+          <t>Primary Fault Memory</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>requestSeed</t>
+          <t>Primary Fault Memory</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>Request</t>
+          <t>Read - number of DTCs</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>requestSeed_Request</t>
+          <t>PrimaryFaultMemory_ReadNumber</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>($27) SecurityAccess - Request seed</t>
+          <t>($19) ReadDtcInformation - Report number of DTC by status mask</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
@@ -6391,7 +6391,7 @@
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>ProgrammingSession, ExtendedDiagnosticSession</t>
+          <t>DefaultSession, ExtendedDiagnosticSession</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>_3164@_3159</t>
+          <t>_3206@_3159</t>
         </is>
       </c>
     </row>
@@ -6413,47 +6413,47 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>27 12</t>
+          <t>19 02</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Security Access</t>
+          <t>Primary Fault Memory</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>sendKey</t>
+          <t>Primary Fault Memory</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>Send</t>
+          <t>Read - DTCs by status mask</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>sendKey_Send</t>
+          <t>PrimaryFaultMemory_ReadAllIdentified</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>($27) SecurityAccess - Send key</t>
+          <t>($19) ReadDtcInformation - Report DTC by status mask</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Physical, Functional</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>ProgrammingSession, ExtendedDiagnosticSession</t>
+          <t>DefaultSession, ExtendedDiagnosticSession</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
@@ -6463,7 +6463,7 @@
       </c>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>_3166@_3159</t>
+          <t>_3207@_3159</t>
         </is>
       </c>
     </row>
@@ -6475,37 +6475,37 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>29 01 00</t>
+          <t>19 03</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Authentication</t>
+          <t>Primary Fault Memory</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>Authentication</t>
+          <t>Primary Fault Memory</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>Verify Certificate Unidirectional</t>
+          <t>Read - snapshot ID</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>Authentication_Verify_Certificate_Unidirectional</t>
+          <t>PrimaryFaultMemory_Read_snapshot_ID</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>($29) Authentication - VerifyCertificateUnidirectional</t>
+          <t>($19) ReadDtcInformation - ReportDtcSnapshotIdentification</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
@@ -6515,17 +6515,17 @@
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>DefaultSession, ExtendedDiagnosticSession</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>_3009@_3159</t>
+          <t>_3210@_3159</t>
         </is>
       </c>
     </row>
@@ -6537,37 +6537,37 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>29 02 00</t>
+          <t>19 04</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Authentication</t>
+          <t>Primary Fault Memory</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>Authentication</t>
+          <t>Primary Fault Memory</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>Verify Certificate Bidirectional</t>
+          <t>Read - snapshot record</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>Authentication_Verify_Certificate_Bidirectional</t>
+          <t>PrimaryFaultMemory_Read_snapshot_record</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>($29) Authentication - VerifyCertificateBidirectional</t>
+          <t>($19) ReadDtcInformation - Report DTC Snapshot Record by DTC Number</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
@@ -6577,17 +6577,17 @@
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>DefaultSession, ExtendedDiagnosticSession</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>_3010@_3159</t>
+          <t>_3209@_3159</t>
         </is>
       </c>
     </row>
@@ -6599,37 +6599,37 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>29 03</t>
+          <t>19 06</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Authentication</t>
+          <t>Primary Fault Memory</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>Authentication</t>
+          <t>Primary Fault Memory</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>Proof Of Ownership</t>
+          <t>Read - extended data record</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>Authentication_Proof_Of_Ownership</t>
+          <t>PrimaryFaultMemory_Read_extended_data_record</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>($29) Authentication - ProofOfOwnership</t>
+          <t>($19) ReadDtcInformation - Report DTC Extended Data Record by DTC Number</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
@@ -6639,17 +6639,17 @@
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>DefaultSession, ExtendedDiagnosticSession</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>_3011@_3159</t>
+          <t>_3208@_3159</t>
         </is>
       </c>
     </row>
@@ -6661,37 +6661,37 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>29 04</t>
+          <t>19 07</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Authentication</t>
+          <t>Primary Fault Memory</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>Authentication</t>
+          <t>Primary Fault Memory</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>Transmit Certificate</t>
+          <t>Read - number of DTCs by severity</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>Authentication_Transmit_Certificate</t>
+          <t>PrimaryFaultMemory_Read_number_of_DTCs_by_severity</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>($29) Authentication - Transmit Certificate</t>
+          <t>($19) ReadDtcInformation - Report number of DTC by severity mask</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
@@ -6701,17 +6701,17 @@
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>DefaultSession, ExtendedDiagnosticSession</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>_3012@_3159</t>
+          <t>_3211@_3159</t>
         </is>
       </c>
     </row>
@@ -6723,37 +6723,37 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>29 00</t>
+          <t>19 08</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Authentication</t>
+          <t>Primary Fault Memory</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>Authentication</t>
+          <t>Primary Fault Memory</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>Deauthentication</t>
+          <t>Read - DTCs by severity</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>Authentication_Deauthentication</t>
+          <t>PrimaryFaultMemory_Read_DTCs_by_severity</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>($29) Authentication - DeAuthentication</t>
+          <t>($19) ReadDtcInformation - Report DTC by severity mask record</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
@@ -6763,17 +6763,17 @@
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>DefaultSession, ExtendedDiagnosticSession</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>_3013@_3159</t>
+          <t>_3212@_3159</t>
         </is>
       </c>
     </row>
@@ -6785,37 +6785,37 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>29 08</t>
+          <t>19 09</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Authentication</t>
+          <t>Primary Fault Memory</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>Authentication</t>
+          <t>Primary Fault Memory</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>Authentication Configuration</t>
+          <t>Read - severity information</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>Authentication_Authentication_Configuration</t>
+          <t>PrimaryFaultMemory_Read_severity_information</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>($29) Authentication - AuthenticationConfiguration</t>
+          <t>($19) ReadDtcInformation - Report severity information of DTC</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
@@ -6825,17 +6825,17 @@
       </c>
       <c r="J103" s="2" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>DefaultSession, ExtendedDiagnosticSession</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>_3014@_3159</t>
+          <t>_3213@_3159</t>
         </is>
       </c>
     </row>
@@ -6847,47 +6847,47 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>28 03</t>
+          <t>19 0A</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Communication Control</t>
+          <t>Primary Fault Memory</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>DisableRxAndTx</t>
+          <t>Primary Fault Memory</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>Read - supported DTCs</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>DisableRxAndTx_Control</t>
+          <t>PrimaryFaultMemory_ReadAllSupported</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>($28) CommunicationControl</t>
+          <t>($19) ReadDtcInformation - Report supported DTC</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>Physical, Functional</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>ExtendedDiagnosticSession</t>
+          <t>DefaultSession, ExtendedDiagnosticSession</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
@@ -6897,7 +6897,7 @@
       </c>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>_3169@_3159</t>
+          <t>_3214@_3159</t>
         </is>
       </c>
     </row>
@@ -6909,57 +6909,57 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>85 01</t>
+          <t>19 0B</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Control DTC Setting</t>
+          <t>Primary Fault Memory</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>Control DTC Setting</t>
+          <t>Primary Fault Memory</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>On</t>
+          <t>Read - first test failed DTC</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>ControlDTCSetting_On</t>
+          <t>PrimaryFaultMemory_Read_first_test_failed_DTC</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>($85) ControlDTCSetting (on)</t>
+          <t>($19) ReadDtcInformation - ReportFirstTestFailedDTC</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>Physical, Functional</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr">
         <is>
-          <t>ExtendedDiagnosticSession</t>
+          <t>DefaultSession, ExtendedDiagnosticSession</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
-          <t>Locked, Unlocked_0x1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>_3021@_3159</t>
+          <t>_3215@_3159</t>
         </is>
       </c>
     </row>
@@ -6971,57 +6971,57 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>85 02</t>
+          <t>19 0C</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Control DTC Setting</t>
+          <t>Primary Fault Memory</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>Control DTC Setting</t>
+          <t>Primary Fault Memory</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>Off</t>
+          <t>Read - first confirmed DTC</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>ControlDTCSetting_Off</t>
+          <t>PrimaryFaultMemory_Read_first_confirmed_DTC</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>($85) ControlDTCSetting (off)</t>
+          <t>($19) ReadDtcInformation - ReportFirstConfirmedDTC</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>Physical, Functional</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
-          <t>ExtendedDiagnosticSession</t>
+          <t>DefaultSession, ExtendedDiagnosticSession</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>Locked, Unlocked_0x1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>_3022@_3159</t>
+          <t>_3216@_3159</t>
         </is>
       </c>
     </row>
@@ -7033,57 +7033,57 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>22 F020</t>
+          <t>19 0D</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>Measurements</t>
+          <t>Primary Fault Memory</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>Read Public Key status</t>
+          <t>Primary Fault Memory</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>Read</t>
+          <t>Read - most recent test failed DTC</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>Read_Public_Key_status_Read</t>
+          <t>PrimaryFaultMemory_Read_most_recent_test_failed_DTC</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>($22) ReadDataByIdentifier</t>
+          <t>($19) ReadDtcInformation - ReportMostRecentTestFailedDTC</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>Physical, Functional</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="J107" s="2" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>DefaultSession, ExtendedDiagnosticSession</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L107" s="2" t="inlineStr">
         <is>
-          <t>_3172@_3159</t>
+          <t>_3217@_3159</t>
         </is>
       </c>
     </row>
@@ -7095,57 +7095,57 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>22 F15B</t>
+          <t>19 0E</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Measurements</t>
+          <t>Primary Fault Memory</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>Read Fingerprint</t>
+          <t>Primary Fault Memory</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>Read</t>
+          <t>Read - most recent confirmed DTC</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>Read_Fingerprint_Read</t>
+          <t>PrimaryFaultMemory_Read_most_recent_confirmed_DTC</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>($22) ReadDataByIdentifier</t>
+          <t>($19) ReadDtcInformation - ReportMostRecentConfirmedDTC</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>Physical, Functional</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>DefaultSession, ExtendedDiagnosticSession</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L108" s="2" t="inlineStr">
         <is>
-          <t>_3173@_3159</t>
+          <t>_3218@_3159</t>
         </is>
       </c>
     </row>
@@ -7157,57 +7157,57 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>22 F180</t>
+          <t>19 14</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>Measurements</t>
+          <t>Primary Fault Memory</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>Boot Software Identification</t>
+          <t>Primary Fault Memory</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>Read</t>
+          <t>Read - fault detection counter</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>Boot_Software_Identification_Read</t>
+          <t>PrimaryFaultMemory_Read_fault_detection_counter</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>($22) ReadDataByIdentifier</t>
+          <t>($19) ReadDtcInformation - ReportDTCFaultDetectionCounter</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t>Physical, Functional</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="J109" s="2" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>DefaultSession, ExtendedDiagnosticSession</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L109" s="2" t="inlineStr">
         <is>
-          <t>_3174@_3159</t>
+          <t>_3219@_3159</t>
         </is>
       </c>
     </row>
@@ -7224,7 +7224,7 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>22 F187</t>
+          <t>22 F020</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
@@ -7234,7 +7234,7 @@
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>Vehicle manufacturer spare part number</t>
+          <t>Read Public Key status</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
@@ -7244,7 +7244,7 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>Vehicle_manufacturer_spare_part_number_Read</t>
+          <t>Read_Public_Key_status_Read</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
@@ -7269,7 +7269,7 @@
       </c>
       <c r="L110" s="2" t="inlineStr">
         <is>
-          <t>_3175@_3159</t>
+          <t>_3172@_3159</t>
         </is>
       </c>
     </row>
@@ -7286,7 +7286,7 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>22 F18A</t>
+          <t>22 F15B</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
@@ -7296,7 +7296,7 @@
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>System supplier identifier</t>
+          <t>Read Fingerprint</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr">
@@ -7306,7 +7306,7 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>System_supplier_identifier_Read</t>
+          <t>Read_Fingerprint_Read</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
@@ -7331,7 +7331,7 @@
       </c>
       <c r="L111" s="2" t="inlineStr">
         <is>
-          <t>_3176@_3159</t>
+          <t>_3173@_3159</t>
         </is>
       </c>
     </row>
@@ -7348,7 +7348,7 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>22 F191</t>
+          <t>22 F180</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>Vehicle manufacturer ECU hardware number</t>
+          <t>Boot Software Identification</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
@@ -7368,7 +7368,7 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>Vehicle_manufacturer_ECU_hardware_number_Read</t>
+          <t>Boot_Software_Identification_Read</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
@@ -7393,7 +7393,7 @@
       </c>
       <c r="L112" s="2" t="inlineStr">
         <is>
-          <t>_3177@_3159</t>
+          <t>_3174@_3159</t>
         </is>
       </c>
     </row>
@@ -7405,42 +7405,42 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>2E</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>2E F021</t>
+          <t>22 F187</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>Stored Data</t>
+          <t>Measurements</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>Write Public Key</t>
+          <t>Vehicle manufacturer spare part number</t>
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>Write</t>
+          <t>Read</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>Write_Public_Key_Write</t>
+          <t>Vehicle_manufacturer_spare_part_number_Read</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>($2E) WriteDataByIdentifier</t>
+          <t>($22) ReadDataByIdentifier</t>
         </is>
       </c>
       <c r="I113" s="2" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Physical, Functional</t>
         </is>
       </c>
       <c r="J113" s="2" t="inlineStr">
@@ -7455,7 +7455,7 @@
       </c>
       <c r="L113" s="2" t="inlineStr">
         <is>
-          <t>_3179@_3159</t>
+          <t>_3175@_3159</t>
         </is>
       </c>
     </row>
@@ -7467,42 +7467,42 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>2E</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>2E F022</t>
+          <t>22 F18A</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>Stored Data</t>
+          <t>Measurements</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>Reset Public Key to Delivery Mode</t>
+          <t>System supplier identifier</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>Write</t>
+          <t>Read</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>Reset_Public_Key_to_Delivery_Mode_Write</t>
+          <t>System_supplier_identifier_Read</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>($2E) WriteDataByIdentifier</t>
+          <t>($22) ReadDataByIdentifier</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Physical, Functional</t>
         </is>
       </c>
       <c r="J114" s="2" t="inlineStr">
@@ -7517,7 +7517,7 @@
       </c>
       <c r="L114" s="2" t="inlineStr">
         <is>
-          <t>_3181@_3159</t>
+          <t>_3176@_3159</t>
         </is>
       </c>
     </row>
@@ -7529,42 +7529,42 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>2E</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>2E F15A</t>
+          <t>22 F191</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>Stored Data</t>
+          <t>Measurements</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>Write Fingerprint</t>
+          <t>Vehicle manufacturer ECU hardware number</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>Write</t>
+          <t>Read</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>Write_Fingerprint_Write</t>
+          <t>Vehicle_manufacturer_ECU_hardware_number_Read</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>($2E) WriteDataByIdentifier</t>
+          <t>($22) ReadDataByIdentifier</t>
         </is>
       </c>
       <c r="I115" s="2" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Physical, Functional</t>
         </is>
       </c>
       <c r="J115" s="2" t="inlineStr">
@@ -7579,7 +7579,7 @@
       </c>
       <c r="L115" s="2" t="inlineStr">
         <is>
-          <t>_3183@_3159</t>
+          <t>_3177@_3159</t>
         </is>
       </c>
     </row>
@@ -7591,37 +7591,37 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>31 01 DD0F</t>
+          <t>27 11</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>Routine Control</t>
+          <t>Security Access</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>Switchover prevention</t>
+          <t>requestSeed</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Request</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>Switchover_prevention_Start</t>
+          <t>requestSeed_Request</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>($31) RoutineControl - Start routine</t>
+          <t>($27) SecurityAccess - Request seed</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr">
@@ -7631,17 +7631,17 @@
       </c>
       <c r="J116" s="2" t="inlineStr">
         <is>
-          <t>ProgrammingSession</t>
+          <t>ProgrammingSession, ExtendedDiagnosticSession</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>Locked, Unlocked_0x11</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L116" s="2" t="inlineStr">
         <is>
-          <t>_3187@_3159</t>
+          <t>_3164@_3159</t>
         </is>
       </c>
     </row>
@@ -7653,37 +7653,37 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>31 01 DD03</t>
+          <t>27 12</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>Routine Control</t>
+          <t>Security Access</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>Version installation</t>
+          <t>sendKey</t>
         </is>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Send</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>Version_installation_Start</t>
+          <t>sendKey_Send</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>($31) RoutineControl - Start routine</t>
+          <t>($27) SecurityAccess - Send key</t>
         </is>
       </c>
       <c r="I117" s="2" t="inlineStr">
@@ -7703,7 +7703,7 @@
       </c>
       <c r="L117" s="2" t="inlineStr">
         <is>
-          <t>_3189@_3159</t>
+          <t>_3166@_3159</t>
         </is>
       </c>
     </row>
@@ -7715,47 +7715,47 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>31 01 DD01</t>
+          <t>28 03</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>Routine Control</t>
+          <t>Communication Control</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>Stay In Boot</t>
+          <t>DisableRxAndTx</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Control</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>Stay_In_Boot_Start</t>
+          <t>DisableRxAndTx_Control</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>($31) RoutineControl - Start routine</t>
+          <t>($28) CommunicationControl</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Physical, Functional</t>
         </is>
       </c>
       <c r="J118" s="2" t="inlineStr">
         <is>
-          <t>ProgrammingSession, ExtendedDiagnosticSession</t>
+          <t>ExtendedDiagnosticSession</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
@@ -7765,7 +7765,7 @@
       </c>
       <c r="L118" s="2" t="inlineStr">
         <is>
-          <t>_3191@_3159</t>
+          <t>_3169@_3159</t>
         </is>
       </c>
     </row>
@@ -7777,37 +7777,37 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>31 01 FF01</t>
+          <t>29 00</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>Routine Control</t>
+          <t>Authentication</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>Programming Dependencies Check</t>
+          <t>Authentication</t>
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Deauthentication</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>Programming_Dependencies_Check_Start</t>
+          <t>Authentication_Deauthentication</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>($31) RoutineControl - Start routine</t>
+          <t>($29) Authentication - DeAuthentication</t>
         </is>
       </c>
       <c r="I119" s="2" t="inlineStr">
@@ -7817,17 +7817,17 @@
       </c>
       <c r="J119" s="2" t="inlineStr">
         <is>
-          <t>ProgrammingSession</t>
+          <t>All</t>
         </is>
       </c>
       <c r="K119" s="2" t="inlineStr">
         <is>
-          <t>Unlocked_0x11</t>
+          <t>All</t>
         </is>
       </c>
       <c r="L119" s="2" t="inlineStr">
         <is>
-          <t>_3193@_3159</t>
+          <t>_3013@_3159</t>
         </is>
       </c>
     </row>
@@ -7839,37 +7839,37 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>31 01 FF00</t>
+          <t>29 01 00</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>Routine Control</t>
+          <t>Authentication</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>EraseMemory</t>
+          <t>Authentication</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Verify Certificate Unidirectional</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>EraseMemory_Start</t>
+          <t>Authentication_Verify_Certificate_Unidirectional</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>($31) RoutineControl - Start routine</t>
+          <t>($29) Authentication - VerifyCertificateUnidirectional</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr">
@@ -7879,17 +7879,17 @@
       </c>
       <c r="J120" s="2" t="inlineStr">
         <is>
-          <t>ProgrammingSession, ExtendedDiagnosticSession</t>
+          <t>All</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>All</t>
         </is>
       </c>
       <c r="L120" s="2" t="inlineStr">
         <is>
-          <t>_3195@_3159</t>
+          <t>_3009@_3159</t>
         </is>
       </c>
     </row>
@@ -7901,37 +7901,37 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>31 01 D005</t>
+          <t>29 02 00</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>Routine Control</t>
+          <t>Authentication</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>Flash File Installation</t>
+          <t>Authentication</t>
         </is>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Verify Certificate Bidirectional</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>Flash_File_Installation_Start</t>
+          <t>Authentication_Verify_Certificate_Bidirectional</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>($31) RoutineControl - Start routine</t>
+          <t>($29) Authentication - VerifyCertificateBidirectional</t>
         </is>
       </c>
       <c r="I121" s="2" t="inlineStr">
@@ -7941,17 +7941,17 @@
       </c>
       <c r="J121" s="2" t="inlineStr">
         <is>
-          <t>ProgrammingSession, ExtendedDiagnosticSession</t>
+          <t>All</t>
         </is>
       </c>
       <c r="K121" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>All</t>
         </is>
       </c>
       <c r="L121" s="2" t="inlineStr">
         <is>
-          <t>_3197@_3159</t>
+          <t>_3010@_3159</t>
         </is>
       </c>
     </row>
@@ -7963,37 +7963,37 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>31 01 DD02</t>
+          <t>29 03</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>Routine Control</t>
+          <t>Authentication</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>Security signature</t>
+          <t>Authentication</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Proof Of Ownership</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>Security_signature_Start</t>
+          <t>Authentication_Proof_Of_Ownership</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>($31) RoutineControl - Start routine</t>
+          <t>($29) Authentication - ProofOfOwnership</t>
         </is>
       </c>
       <c r="I122" s="2" t="inlineStr">
@@ -8003,17 +8003,17 @@
       </c>
       <c r="J122" s="2" t="inlineStr">
         <is>
-          <t>ProgrammingSession, ExtendedDiagnosticSession</t>
+          <t>All</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>All</t>
         </is>
       </c>
       <c r="L122" s="2" t="inlineStr">
         <is>
-          <t>_3199@_3159</t>
+          <t>_3011@_3159</t>
         </is>
       </c>
     </row>
@@ -8025,37 +8025,37 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>31 01 0203</t>
+          <t>29 04</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>Routine Control</t>
+          <t>Authentication</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>Programming Precondition Check</t>
+          <t>Authentication</t>
         </is>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Transmit Certificate</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>Programming_Precondition_Check_Start</t>
+          <t>Authentication_Transmit_Certificate</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>($31) RoutineControl - Start routine</t>
+          <t>($29) Authentication - Transmit Certificate</t>
         </is>
       </c>
       <c r="I123" s="2" t="inlineStr">
@@ -8065,17 +8065,17 @@
       </c>
       <c r="J123" s="2" t="inlineStr">
         <is>
-          <t>ExtendedDiagnosticSession</t>
+          <t>All</t>
         </is>
       </c>
       <c r="K123" s="2" t="inlineStr">
         <is>
-          <t>Locked</t>
+          <t>All</t>
         </is>
       </c>
       <c r="L123" s="2" t="inlineStr">
         <is>
-          <t>_3201@_3159</t>
+          <t>_3012@_3159</t>
         </is>
       </c>
     </row>
@@ -8087,37 +8087,37 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>31 01 DD04</t>
+          <t>29 08</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>Routine Control</t>
+          <t>Authentication</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>Version switchover</t>
+          <t>Authentication</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Authentication Configuration</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>Version_switchover_Start</t>
+          <t>Authentication_Authentication_Configuration</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>($31) RoutineControl - Start routine</t>
+          <t>($29) Authentication - AuthenticationConfiguration</t>
         </is>
       </c>
       <c r="I124" s="2" t="inlineStr">
@@ -8127,17 +8127,17 @@
       </c>
       <c r="J124" s="2" t="inlineStr">
         <is>
-          <t>ProgrammingSession, ExtendedDiagnosticSession</t>
+          <t>All</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>Unlocked_0x11, Unlocked_0x1</t>
+          <t>All</t>
         </is>
       </c>
       <c r="L124" s="2" t="inlineStr">
         <is>
-          <t>_3203@_3159</t>
+          <t>_3014@_3159</t>
         </is>
       </c>
     </row>
@@ -8149,37 +8149,37 @@
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>2E</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>31 03 DD04</t>
+          <t>2E F021</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>Routine Control</t>
+          <t>Stored Data</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>Version switchover</t>
+          <t>Write Public Key</t>
         </is>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>Request Results</t>
+          <t>Write</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>Version_switchover_RequestResults</t>
+          <t>Write_Public_Key_Write</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>($31) RoutineControl - Request routine results</t>
+          <t>($2E) WriteDataByIdentifier</t>
         </is>
       </c>
       <c r="I125" s="2" t="inlineStr">
@@ -8189,17 +8189,17 @@
       </c>
       <c r="J125" s="2" t="inlineStr">
         <is>
-          <t>ProgrammingSession, ExtendedDiagnosticSession</t>
+          <t>All</t>
         </is>
       </c>
       <c r="K125" s="2" t="inlineStr">
         <is>
-          <t>Unlocked_0x11, Unlocked_0x1</t>
+          <t>All</t>
         </is>
       </c>
       <c r="L125" s="2" t="inlineStr">
         <is>
-          <t>_3204@_3159</t>
+          <t>_3179@_3159</t>
         </is>
       </c>
     </row>
@@ -8211,37 +8211,37 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>2E</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>19 01</t>
+          <t>2E F022</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>Primary Fault Memory</t>
+          <t>Stored Data</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>Primary Fault Memory</t>
+          <t>Reset Public Key to Delivery Mode</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>Read - number of DTCs</t>
+          <t>Write</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>PrimaryFaultMemory_ReadNumber</t>
+          <t>Reset_Public_Key_to_Delivery_Mode_Write</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>($19) ReadDtcInformation - Report number of DTC by status mask</t>
+          <t>($2E) WriteDataByIdentifier</t>
         </is>
       </c>
       <c r="I126" s="2" t="inlineStr">
@@ -8251,17 +8251,17 @@
       </c>
       <c r="J126" s="2" t="inlineStr">
         <is>
-          <t>DefaultSession, ExtendedDiagnosticSession</t>
+          <t>All</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>All</t>
         </is>
       </c>
       <c r="L126" s="2" t="inlineStr">
         <is>
-          <t>_3206@_3159</t>
+          <t>_3181@_3159</t>
         </is>
       </c>
     </row>
@@ -8273,57 +8273,57 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>2E</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>19 02</t>
+          <t>2E F15A</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>Primary Fault Memory</t>
+          <t>Stored Data</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>Primary Fault Memory</t>
+          <t>Write Fingerprint</t>
         </is>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>Read - DTCs by status mask</t>
+          <t>Write</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>PrimaryFaultMemory_ReadAllIdentified</t>
+          <t>Write_Fingerprint_Write</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>($19) ReadDtcInformation - Report DTC by status mask</t>
+          <t>($2E) WriteDataByIdentifier</t>
         </is>
       </c>
       <c r="I127" s="2" t="inlineStr">
         <is>
-          <t>Physical, Functional</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="J127" s="2" t="inlineStr">
         <is>
-          <t>DefaultSession, ExtendedDiagnosticSession</t>
+          <t>All</t>
         </is>
       </c>
       <c r="K127" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>All</t>
         </is>
       </c>
       <c r="L127" s="2" t="inlineStr">
         <is>
-          <t>_3207@_3159</t>
+          <t>_3183@_3159</t>
         </is>
       </c>
     </row>
@@ -8335,37 +8335,37 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>19 06</t>
+          <t>31 01 0203</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>Primary Fault Memory</t>
+          <t>Routine Control</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>Primary Fault Memory</t>
+          <t>Programming Precondition Check</t>
         </is>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>Read - extended data record</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>PrimaryFaultMemory_Read_extended_data_record</t>
+          <t>Programming_Precondition_Check_Start</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>($19) ReadDtcInformation - Report DTC Extended Data Record by DTC Number</t>
+          <t>($31) RoutineControl - Start routine</t>
         </is>
       </c>
       <c r="I128" s="2" t="inlineStr">
@@ -8375,17 +8375,17 @@
       </c>
       <c r="J128" s="2" t="inlineStr">
         <is>
-          <t>DefaultSession, ExtendedDiagnosticSession</t>
+          <t>ExtendedDiagnosticSession</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Locked</t>
         </is>
       </c>
       <c r="L128" s="2" t="inlineStr">
         <is>
-          <t>_3208@_3159</t>
+          <t>_3201@_3159</t>
         </is>
       </c>
     </row>
@@ -8397,37 +8397,37 @@
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>19 04</t>
+          <t>31 01 D005</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>Primary Fault Memory</t>
+          <t>Routine Control</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>Primary Fault Memory</t>
+          <t>Flash File Installation</t>
         </is>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>Read - snapshot record</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>PrimaryFaultMemory_Read_snapshot_record</t>
+          <t>Flash_File_Installation_Start</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>($19) ReadDtcInformation - Report DTC Snapshot Record by DTC Number</t>
+          <t>($31) RoutineControl - Start routine</t>
         </is>
       </c>
       <c r="I129" s="2" t="inlineStr">
@@ -8437,7 +8437,7 @@
       </c>
       <c r="J129" s="2" t="inlineStr">
         <is>
-          <t>DefaultSession, ExtendedDiagnosticSession</t>
+          <t>ProgrammingSession, ExtendedDiagnosticSession</t>
         </is>
       </c>
       <c r="K129" s="2" t="inlineStr">
@@ -8447,7 +8447,7 @@
       </c>
       <c r="L129" s="2" t="inlineStr">
         <is>
-          <t>_3209@_3159</t>
+          <t>_3197@_3159</t>
         </is>
       </c>
     </row>
@@ -8459,37 +8459,37 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>19 03</t>
+          <t>31 01 DD01</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>Primary Fault Memory</t>
+          <t>Routine Control</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>Primary Fault Memory</t>
+          <t>Stay In Boot</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>Read - snapshot ID</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>PrimaryFaultMemory_Read_snapshot_ID</t>
+          <t>Stay_In_Boot_Start</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>($19) ReadDtcInformation - ReportDtcSnapshotIdentification</t>
+          <t>($31) RoutineControl - Start routine</t>
         </is>
       </c>
       <c r="I130" s="2" t="inlineStr">
@@ -8499,7 +8499,7 @@
       </c>
       <c r="J130" s="2" t="inlineStr">
         <is>
-          <t>DefaultSession, ExtendedDiagnosticSession</t>
+          <t>ProgrammingSession, ExtendedDiagnosticSession</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr">
@@ -8509,7 +8509,7 @@
       </c>
       <c r="L130" s="2" t="inlineStr">
         <is>
-          <t>_3210@_3159</t>
+          <t>_3191@_3159</t>
         </is>
       </c>
     </row>
@@ -8521,37 +8521,37 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>19 07</t>
+          <t>31 01 DD02</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>Primary Fault Memory</t>
+          <t>Routine Control</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>Primary Fault Memory</t>
+          <t>Security signature</t>
         </is>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>Read - number of DTCs by severity</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>PrimaryFaultMemory_Read_number_of_DTCs_by_severity</t>
+          <t>Security_signature_Start</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t>($19) ReadDtcInformation - Report number of DTC by severity mask</t>
+          <t>($31) RoutineControl - Start routine</t>
         </is>
       </c>
       <c r="I131" s="2" t="inlineStr">
@@ -8561,7 +8561,7 @@
       </c>
       <c r="J131" s="2" t="inlineStr">
         <is>
-          <t>DefaultSession, ExtendedDiagnosticSession</t>
+          <t>ProgrammingSession, ExtendedDiagnosticSession</t>
         </is>
       </c>
       <c r="K131" s="2" t="inlineStr">
@@ -8571,7 +8571,7 @@
       </c>
       <c r="L131" s="2" t="inlineStr">
         <is>
-          <t>_3211@_3159</t>
+          <t>_3199@_3159</t>
         </is>
       </c>
     </row>
@@ -8583,37 +8583,37 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>19 08</t>
+          <t>31 01 DD03</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>Primary Fault Memory</t>
+          <t>Routine Control</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>Primary Fault Memory</t>
+          <t>Version installation</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>Read - DTCs by severity</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>PrimaryFaultMemory_Read_DTCs_by_severity</t>
+          <t>Version_installation_Start</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>($19) ReadDtcInformation - Report DTC by severity mask record</t>
+          <t>($31) RoutineControl - Start routine</t>
         </is>
       </c>
       <c r="I132" s="2" t="inlineStr">
@@ -8623,7 +8623,7 @@
       </c>
       <c r="J132" s="2" t="inlineStr">
         <is>
-          <t>DefaultSession, ExtendedDiagnosticSession</t>
+          <t>ProgrammingSession, ExtendedDiagnosticSession</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="L132" s="2" t="inlineStr">
         <is>
-          <t>_3212@_3159</t>
+          <t>_3189@_3159</t>
         </is>
       </c>
     </row>
@@ -8645,37 +8645,37 @@
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>19 09</t>
+          <t>31 01 DD04</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>Primary Fault Memory</t>
+          <t>Routine Control</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>Primary Fault Memory</t>
+          <t>Version switchover</t>
         </is>
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>Read - severity information</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>PrimaryFaultMemory_Read_severity_information</t>
+          <t>Version_switchover_Start</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t>($19) ReadDtcInformation - Report severity information of DTC</t>
+          <t>($31) RoutineControl - Start routine</t>
         </is>
       </c>
       <c r="I133" s="2" t="inlineStr">
@@ -8685,17 +8685,17 @@
       </c>
       <c r="J133" s="2" t="inlineStr">
         <is>
-          <t>DefaultSession, ExtendedDiagnosticSession</t>
+          <t>ProgrammingSession, ExtendedDiagnosticSession</t>
         </is>
       </c>
       <c r="K133" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Unlocked_0x11, Unlocked_0x1</t>
         </is>
       </c>
       <c r="L133" s="2" t="inlineStr">
         <is>
-          <t>_3213@_3159</t>
+          <t>_3203@_3159</t>
         </is>
       </c>
     </row>
@@ -8707,37 +8707,37 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>19 0A</t>
+          <t>31 01 DD0F</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>Primary Fault Memory</t>
+          <t>Routine Control</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>Primary Fault Memory</t>
+          <t>Switchover prevention</t>
         </is>
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>Read - supported DTCs</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>PrimaryFaultMemory_ReadAllSupported</t>
+          <t>Switchover_prevention_Start</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>($19) ReadDtcInformation - Report supported DTC</t>
+          <t>($31) RoutineControl - Start routine</t>
         </is>
       </c>
       <c r="I134" s="2" t="inlineStr">
@@ -8747,17 +8747,17 @@
       </c>
       <c r="J134" s="2" t="inlineStr">
         <is>
-          <t>DefaultSession, ExtendedDiagnosticSession</t>
+          <t>ProgrammingSession</t>
         </is>
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Locked, Unlocked_0x11</t>
         </is>
       </c>
       <c r="L134" s="2" t="inlineStr">
         <is>
-          <t>_3214@_3159</t>
+          <t>_3187@_3159</t>
         </is>
       </c>
     </row>
@@ -8769,37 +8769,37 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>19 0B</t>
+          <t>31 01 FF00</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>Primary Fault Memory</t>
+          <t>Routine Control</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>Primary Fault Memory</t>
+          <t>EraseMemory</t>
         </is>
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>Read - first test failed DTC</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>PrimaryFaultMemory_Read_first_test_failed_DTC</t>
+          <t>EraseMemory_Start</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t>($19) ReadDtcInformation - ReportFirstTestFailedDTC</t>
+          <t>($31) RoutineControl - Start routine</t>
         </is>
       </c>
       <c r="I135" s="2" t="inlineStr">
@@ -8809,7 +8809,7 @@
       </c>
       <c r="J135" s="2" t="inlineStr">
         <is>
-          <t>DefaultSession, ExtendedDiagnosticSession</t>
+          <t>ProgrammingSession, ExtendedDiagnosticSession</t>
         </is>
       </c>
       <c r="K135" s="2" t="inlineStr">
@@ -8819,7 +8819,7 @@
       </c>
       <c r="L135" s="2" t="inlineStr">
         <is>
-          <t>_3215@_3159</t>
+          <t>_3195@_3159</t>
         </is>
       </c>
     </row>
@@ -8831,37 +8831,37 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>19 0C</t>
+          <t>31 01 FF01</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>Primary Fault Memory</t>
+          <t>Routine Control</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>Primary Fault Memory</t>
+          <t>Programming Dependencies Check</t>
         </is>
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>Read - first confirmed DTC</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>PrimaryFaultMemory_Read_first_confirmed_DTC</t>
+          <t>Programming_Dependencies_Check_Start</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>($19) ReadDtcInformation - ReportFirstConfirmedDTC</t>
+          <t>($31) RoutineControl - Start routine</t>
         </is>
       </c>
       <c r="I136" s="2" t="inlineStr">
@@ -8871,17 +8871,17 @@
       </c>
       <c r="J136" s="2" t="inlineStr">
         <is>
-          <t>DefaultSession, ExtendedDiagnosticSession</t>
+          <t>ProgrammingSession</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Unlocked_0x11</t>
         </is>
       </c>
       <c r="L136" s="2" t="inlineStr">
         <is>
-          <t>_3216@_3159</t>
+          <t>_3193@_3159</t>
         </is>
       </c>
     </row>
@@ -8893,37 +8893,37 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>19 0D</t>
+          <t>31 03 DD04</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>Primary Fault Memory</t>
+          <t>Routine Control</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>Primary Fault Memory</t>
+          <t>Version switchover</t>
         </is>
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>Read - most recent test failed DTC</t>
+          <t>Request Results</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>PrimaryFaultMemory_Read_most_recent_test_failed_DTC</t>
+          <t>Version_switchover_RequestResults</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
-          <t>($19) ReadDtcInformation - ReportMostRecentTestFailedDTC</t>
+          <t>($31) RoutineControl - Request routine results</t>
         </is>
       </c>
       <c r="I137" s="2" t="inlineStr">
@@ -8933,17 +8933,17 @@
       </c>
       <c r="J137" s="2" t="inlineStr">
         <is>
-          <t>DefaultSession, ExtendedDiagnosticSession</t>
+          <t>ProgrammingSession, ExtendedDiagnosticSession</t>
         </is>
       </c>
       <c r="K137" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Unlocked_0x11, Unlocked_0x1</t>
         </is>
       </c>
       <c r="L137" s="2" t="inlineStr">
         <is>
-          <t>_3217@_3159</t>
+          <t>_3204@_3159</t>
         </is>
       </c>
     </row>
@@ -8955,57 +8955,57 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>3E</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>19 0E</t>
+          <t>3E 00</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>Primary Fault Memory</t>
+          <t>Tester Present</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>Primary Fault Memory</t>
+          <t>Tester Present</t>
         </is>
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>Read - most recent confirmed DTC</t>
+          <t>Send</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>PrimaryFaultMemory_Read_most_recent_confirmed_DTC</t>
+          <t>TesterPresent_Send</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t>($19) ReadDtcInformation - ReportMostRecentConfirmedDTC</t>
+          <t>($3E) TesterPresent</t>
         </is>
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Physical, Functional</t>
         </is>
       </c>
       <c r="J138" s="2" t="inlineStr">
         <is>
-          <t>DefaultSession, ExtendedDiagnosticSession</t>
+          <t>All</t>
         </is>
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>All</t>
         </is>
       </c>
       <c r="L138" s="2" t="inlineStr">
         <is>
-          <t>_3218@_3159</t>
+          <t>_3004@_3159</t>
         </is>
       </c>
     </row>
@@ -9017,57 +9017,57 @@
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>85</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>19 14</t>
+          <t>85 01</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>Primary Fault Memory</t>
+          <t>Control DTC Setting</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>Primary Fault Memory</t>
+          <t>Control DTC Setting</t>
         </is>
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>Read - fault detection counter</t>
+          <t>On</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>PrimaryFaultMemory_Read_fault_detection_counter</t>
+          <t>ControlDTCSetting_On</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
-          <t>($19) ReadDtcInformation - ReportDTCFaultDetectionCounter</t>
+          <t>($85) ControlDTCSetting (on)</t>
         </is>
       </c>
       <c r="I139" s="2" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Physical, Functional</t>
         </is>
       </c>
       <c r="J139" s="2" t="inlineStr">
         <is>
-          <t>DefaultSession, ExtendedDiagnosticSession</t>
+          <t>ExtendedDiagnosticSession</t>
         </is>
       </c>
       <c r="K139" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Locked, Unlocked_0x1</t>
         </is>
       </c>
       <c r="L139" s="2" t="inlineStr">
         <is>
-          <t>_3219@_3159</t>
+          <t>_3021@_3159</t>
         </is>
       </c>
     </row>
@@ -9079,37 +9079,37 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>85</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>85 02</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>Primary Fault Memory</t>
+          <t>Control DTC Setting</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>Primary Fault Memory</t>
+          <t>Control DTC Setting</t>
         </is>
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>Clear DTC</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>PrimaryFaultMemory_Clear</t>
+          <t>ControlDTCSetting_Off</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>($14) ClearDiagnosticInformation</t>
+          <t>($85) ControlDTCSetting (off)</t>
         </is>
       </c>
       <c r="I140" s="2" t="inlineStr">
@@ -9119,17 +9119,17 @@
       </c>
       <c r="J140" s="2" t="inlineStr">
         <is>
-          <t>DefaultSession, ExtendedDiagnosticSession</t>
+          <t>ExtendedDiagnosticSession</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Locked, Unlocked_0x1</t>
         </is>
       </c>
       <c r="L140" s="2" t="inlineStr">
         <is>
-          <t>_3220@_3159</t>
+          <t>_3022@_3159</t>
         </is>
       </c>
     </row>
@@ -25086,42 +25086,263 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
+          <t>0601</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Sensor Alignment SDC Control</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Sensor_Alignment_SDC_Control</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Routine Control</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>ExtendedDiagnosticSession</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Start: 31 01 0601
+Stop: 31 02 0601
+Request Results: 31 03 0601</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Results: SDC Progress, SDC Status, Velocity Too High, Velocity Too Low, Yaw Rate Too High, Acceleration Too High, Rain Detect, Interference Threshold Too High, Paused by Diag, Paused by Cust, Blindness Detected, Invalid Communication, Invalid Detection List, Invalid Input, SDC azimuth angle, SDC elevation angle, SDC roll angle</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>_3048@_2995</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Base Variant</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>0602</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Sensor Alignment EOLC Control</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Sensor_Alignment_EOLC_Control</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Routine Control</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>ExtendedDiagnosticSession</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Start: 31 01 0602
+Stop: 31 02 0602
+Request Results: 31 03 0602</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Control Options (Start): EOLC Mode, EOLC Measurement Type, EOLC Reference Type, DopplerPositionXEOL, DopplerPositionYEOL, DopplerPositionZEOL
+Results: EOLC_Status, Azimuth_Angle, Elevation_Angle, Target Average Azimuth Angle, Target Average Elevation Angle, Target Average Distance, Target Average Signal Power, Target Average SNR, Target Average Speed, Target Average Azimuth Angle Standard Deviation, Target Average Elevation Angle Standard Deviation, Target Average Speed Standard Deviation, Target Average Azimuth Angle Quality, Target Average Elevation Angle Quality, Target Quality Indicator</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>_3044@_2995</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Base Variant</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Sensor Alignment AIC Control</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Sensor_Alignment_AIC_Control</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Routine Control</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>ExtendedDiagnosticSession</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Start: 31 01 0603
+Stop: 31 02 0603
+Request Results: 31 03 0603</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>Results: AIC Progress, AIC Status, AIC azimuth angle, AIC elevation angle, AIC roll angle, Velocity Too High, Velocity Too Low, Yaw Rate Too High, Acceleration Too High, Rain Detect, Interference Threshold Too High, Paused by Diag, Paused by Cust, Blindness Detected, Invalid Communication, Invalid Detection List, Invalid Input</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>_3040@_2995</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Base Variant</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>0604</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Sensor Alignment CDC Control</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Sensor_Alignment_CDC_Control</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Routine Control</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>ExtendedDiagnosticSession</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Start: 31 01 0604
+Stop: 31 02 0604
+Request Results: 31 03 0604</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Results: CDC Progress, CDC Status, CDC azimuth angle, CDC elevation angle, CDC roll angle, Velocity Too High, Velocity Too Low, Yaw Rate Too High, Acceleration Too High, Rain Detect, Interference Threshold Too High, Paused by Diag, Paused by Cust, Blindness Detected, Invalid Communication, Invalid Detection List, Invalid Input</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>_3036@_2995</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Base Variant</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>0650</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>Bumper Repair Validation Control</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Bumper_Repair_Validation_Control</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Routine Control</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>ExtendedDiagnosticSession</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Start: 31 01 0650
 Stop: 31 02 0650
 Request Results: 31 03 0650</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>Control Options (Start): Maximum Radius, Minimum Radius, Minimum Number of events
 Status (Start): routineinfo
@@ -25129,231 +25350,10 @@
 Results: routineinfo, Average RCS Overall, Sector Information, Odometer Value, Bumper Validation Overall Status, Bumper Validation Error Info</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr"/>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>_3032@_2995</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Base Variant</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>0604</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Sensor Alignment CDC Control</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Sensor_Alignment_CDC_Control</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Routine Control</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>ExtendedDiagnosticSession</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Start: 31 01 0604
-Stop: 31 02 0604
-Request Results: 31 03 0604</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>Results: CDC Progress, CDC Status, CDC azimuth angle, CDC elevation angle, CDC roll angle, Velocity Too High, Velocity Too Low, Yaw Rate Too High, Acceleration Too High, Rain Detect, Interference Threshold Too High, Paused by Diag, Paused by Cust, Blindness Detected, Invalid Communication, Invalid Detection List, Invalid Input</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr"/>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>_3036@_2995</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Base Variant</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>0603</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Sensor Alignment AIC Control</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Sensor_Alignment_AIC_Control</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Routine Control</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>ExtendedDiagnosticSession</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Start: 31 01 0603
-Stop: 31 02 0603
-Request Results: 31 03 0603</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>Results: AIC Progress, AIC Status, AIC azimuth angle, AIC elevation angle, AIC roll angle, Velocity Too High, Velocity Too Low, Yaw Rate Too High, Acceleration Too High, Rain Detect, Interference Threshold Too High, Paused by Diag, Paused by Cust, Blindness Detected, Invalid Communication, Invalid Detection List, Invalid Input</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr"/>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>_3040@_2995</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Base Variant</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>0602</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Sensor Alignment EOLC Control</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Sensor_Alignment_EOLC_Control</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Routine Control</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>ExtendedDiagnosticSession</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>Start: 31 01 0602
-Stop: 31 02 0602
-Request Results: 31 03 0602</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>Control Options (Start): EOLC Mode, EOLC Measurement Type, EOLC Reference Type, DopplerPositionXEOL, DopplerPositionYEOL, DopplerPositionZEOL
-Results: EOLC_Status, Azimuth_Angle, Elevation_Angle, Target Average Azimuth Angle, Target Average Elevation Angle, Target Average Distance, Target Average Signal Power, Target Average SNR, Target Average Speed, Target Average Azimuth Angle Standard Deviation, Target Average Elevation Angle Standard Deviation, Target Average Speed Standard Deviation, Target Average Azimuth Angle Quality, Target Average Elevation Angle Quality, Target Quality Indicator</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr"/>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>_3044@_2995</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Base Variant</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>0601</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Sensor Alignment SDC Control</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Sensor_Alignment_SDC_Control</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Routine Control</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>ExtendedDiagnosticSession</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>Start: 31 01 0601
-Stop: 31 02 0601
-Request Results: 31 03 0601</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>Results: SDC Progress, SDC Status, Velocity Too High, Velocity Too Low, Yaw Rate Too High, Acceleration Too High, Rain Detect, Interference Threshold Too High, Paused by Diag, Paused by Cust, Blindness Detected, Invalid Communication, Invalid Detection List, Invalid Input, SDC azimuth angle, SDC elevation angle, SDC roll angle</t>
-        </is>
-      </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>_3048@_2995</t>
+          <t>_3032@_2995</t>
         </is>
       </c>
     </row>
@@ -25531,17 +25531,17 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>DD0F</t>
+          <t>0203</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Switchover prevention</t>
+          <t>Programming Precondition Check</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Switchover_prevention</t>
+          <t>Programming_Precondition_Check</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -25551,24 +25551,28 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>ProgrammingSession</t>
+          <t>ExtendedDiagnosticSession</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Locked, Unlocked_0x11</t>
+          <t>Locked</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Start: 31 01 DD0F</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr"/>
+          <t>Start: 31 01 0203</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>Status (Start): Routine Result</t>
+        </is>
+      </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>_3186@_3159</t>
+          <t>_3200@_3159</t>
         </is>
       </c>
     </row>
@@ -25580,17 +25584,17 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>DD03</t>
+          <t>D005</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Version installation</t>
+          <t>Flash File Installation</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Version_installation</t>
+          <t>Flash_File_Installation</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -25610,14 +25614,14 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Start: 31 01 DD03</t>
+          <t>Start: 31 01 D005</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr"/>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>_3188@_3159</t>
+          <t>_3196@_3159</t>
         </is>
       </c>
     </row>
@@ -25678,17 +25682,17 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>FF01</t>
+          <t>DD02</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Programming Dependencies Check</t>
+          <t>Security signature</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Programming_Dependencies_Check</t>
+          <t>Security_signature</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -25698,28 +25702,24 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>ProgrammingSession</t>
+          <t>ProgrammingSession, ExtendedDiagnosticSession</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Unlocked_0x11</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Start: 31 01 FF01</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>Status (Start): Check Programming Dependencies Status</t>
-        </is>
-      </c>
+          <t>Start: 31 01 DD02</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr"/>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>_3192@_3159</t>
+          <t>_3198@_3159</t>
         </is>
       </c>
     </row>
@@ -25731,17 +25731,17 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>FF00</t>
+          <t>DD03</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>EraseMemory</t>
+          <t>Version installation</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>EraseMemory</t>
+          <t>Version_installation</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -25761,14 +25761,14 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Start: 31 01 FF00</t>
+          <t>Start: 31 01 DD03</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr"/>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>_3194@_3159</t>
+          <t>_3188@_3159</t>
         </is>
       </c>
     </row>
@@ -25780,17 +25780,17 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>D005</t>
+          <t>DD04</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Flash File Installation</t>
+          <t>Version switchover</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Flash_File_Installation</t>
+          <t>Version_switchover</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -25805,19 +25805,25 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Unlocked_0x11, Unlocked_0x1</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Start: 31 01 D005</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr"/>
+          <t>Start: 31 01 DD04
+Request Results: 31 03 DD04</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>Status (Start): Version Switch Result
+Results: Version Switch Result</t>
+        </is>
+      </c>
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>_3196@_3159</t>
+          <t>_3202@_3159</t>
         </is>
       </c>
     </row>
@@ -25829,17 +25835,17 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>DD02</t>
+          <t>DD0F</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Security signature</t>
+          <t>Switchover prevention</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Security_signature</t>
+          <t>Switchover_prevention</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -25849,24 +25855,24 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>ProgrammingSession, ExtendedDiagnosticSession</t>
+          <t>ProgrammingSession</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Locked, Unlocked_0x11</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Start: 31 01 DD02</t>
+          <t>Start: 31 01 DD0F</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr"/>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>_3198@_3159</t>
+          <t>_3186@_3159</t>
         </is>
       </c>
     </row>
@@ -25878,17 +25884,17 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>0203</t>
+          <t>FF00</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Programming Precondition Check</t>
+          <t>EraseMemory</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Programming_Precondition_Check</t>
+          <t>EraseMemory</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -25898,28 +25904,24 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>ExtendedDiagnosticSession</t>
+          <t>ProgrammingSession, ExtendedDiagnosticSession</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Locked</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Start: 31 01 0203</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>Status (Start): Routine Result</t>
-        </is>
-      </c>
+          <t>Start: 31 01 FF00</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr"/>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>_3200@_3159</t>
+          <t>_3194@_3159</t>
         </is>
       </c>
     </row>
@@ -25931,17 +25933,17 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>DD04</t>
+          <t>FF01</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Version switchover</t>
+          <t>Programming Dependencies Check</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Version_switchover</t>
+          <t>Programming_Dependencies_Check</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -25951,30 +25953,28 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>ProgrammingSession, ExtendedDiagnosticSession</t>
+          <t>ProgrammingSession</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Unlocked_0x11, Unlocked_0x1</t>
+          <t>Unlocked_0x11</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Start: 31 01 DD04
-Request Results: 31 03 DD04</t>
+          <t>Start: 31 01 FF01</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>Status (Start): Version Switch Result
-Results: Version Switch Result</t>
+          <t>Status (Start): Check Programming Dependencies Status</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>_3202@_3159</t>
+          <t>_3192@_3159</t>
         </is>
       </c>
     </row>
